--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,37 +58,142 @@
     <t>Link 2</t>
   </si>
   <si>
+    <t>Laatst bijgewerkt: 2025-09-05 14:53:33</t>
+  </si>
+  <si>
+    <t>Chicago Fire vs New England Revolution</t>
+  </si>
+  <si>
+    <t>Montenegro vs Tsjechië</t>
+  </si>
+  <si>
     <t>Oekraïne vs Frankrijk</t>
   </si>
   <si>
+    <t>IJsland vs Azerbeidzjan</t>
+  </si>
+  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
     <t>wedstrijd</t>
   </si>
   <si>
-    <t>meer dan 7.5</t>
+    <t>montenegro</t>
+  </si>
+  <si>
+    <t>oekraïne</t>
+  </si>
+  <si>
+    <t>azerbeidzjan</t>
+  </si>
+  <si>
+    <t>meer dan 10.5</t>
+  </si>
+  <si>
+    <t>meer dan 3.5</t>
+  </si>
+  <si>
+    <t>meer dan 2.5</t>
+  </si>
+  <si>
+    <t>meer dan 8.5</t>
+  </si>
+  <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
+    <t>onecasino</t>
+  </si>
+  <si>
+    <t>jacks</t>
   </si>
   <si>
     <t>toto</t>
   </si>
   <si>
-    <t>minder dan 7.5</t>
-  </si>
-  <si>
-    <t>onecasino</t>
-  </si>
-  <si>
-    <t>1=92, 2=58</t>
-  </si>
-  <si>
-    <t>€1.38</t>
+    <t>minder dan 10.5</t>
+  </si>
+  <si>
+    <t>minder dan 3.5</t>
+  </si>
+  <si>
+    <t>minder dan 2.5</t>
+  </si>
+  <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
+    <t>minder dan 9.5</t>
+  </si>
+  <si>
+    <t>starcasino</t>
+  </si>
+  <si>
+    <t>1=58, 2=92</t>
+  </si>
+  <si>
+    <t>1=60, 2=90</t>
+  </si>
+  <si>
+    <t>1=44, 2=106</t>
+  </si>
+  <si>
+    <t>1=66, 2=84</t>
+  </si>
+  <si>
+    <t>1=93, 2=57</t>
+  </si>
+  <si>
+    <t>1=74, 2=76</t>
+  </si>
+  <si>
+    <t>1=55, 2=95</t>
+  </si>
+  <si>
+    <t>€8.92</t>
+  </si>
+  <si>
+    <t>€5.46</t>
+  </si>
+  <si>
+    <t>€3.12</t>
+  </si>
+  <si>
+    <t>€2.73</t>
+  </si>
+  <si>
+    <t>€2.0</t>
+  </si>
+  <si>
+    <t>€1.7</t>
+  </si>
+  <si>
+    <t>€1.25</t>
+  </si>
+  <si>
+    <t>https://sports.onecasino.nl/#/event/10025497</t>
+  </si>
+  <si>
+    <t>https://jacks.nl/sports/event/1023168639#event/1023168639</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590797</t>
   </si>
   <si>
-    <t>https://sports.onecasino.nl/#/event/9930916</t>
+    <t>https://jacks.nl/sports/event/1022335870#event/1022335870</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=11998073</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549442</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623890</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623891</t>
   </si>
 </sst>
 </file>
@@ -459,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -510,50 +615,377 @@
       <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3">
+        <v>2.74</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3">
+        <v>1.75</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3">
+        <v>6.36</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4">
+        <v>2.6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4">
+        <v>1.7273</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4">
+        <v>3.64</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5">
+        <v>3.5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>1.4445</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5">
+        <v>2.2</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>2.33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>1.8182</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6">
+        <v>2.08</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7">
         <v>1.65</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7">
+        <v>2.6667</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7">
+        <v>1.89</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>2.05</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8">
+        <v>1.22</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="I2">
-        <v>2.61</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>1.08</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>24</v>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>2.05</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9">
+        <v>1.22</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10">
+        <v>2.75</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10">
+        <v>1.14</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M2" r:id="rId1"/>
-    <hyperlink ref="N2" r:id="rId2" location="/event/9930916"/>
+    <hyperlink ref="M3" r:id="rId1" location="/event/10025497"/>
+    <hyperlink ref="N3" r:id="rId2"/>
+    <hyperlink ref="M4" r:id="rId3" location="event/1023168639"/>
+    <hyperlink ref="N4" r:id="rId4"/>
+    <hyperlink ref="M5" r:id="rId5"/>
+    <hyperlink ref="N5" r:id="rId6"/>
+    <hyperlink ref="M6" r:id="rId7" location="event/1022335870"/>
+    <hyperlink ref="N6" r:id="rId8"/>
+    <hyperlink ref="M7" r:id="rId9" location="event/1023168639"/>
+    <hyperlink ref="N7" r:id="rId10"/>
+    <hyperlink ref="M8" r:id="rId11"/>
+    <hyperlink ref="N8" r:id="rId12"/>
+    <hyperlink ref="M9" r:id="rId13"/>
+    <hyperlink ref="N9" r:id="rId14"/>
+    <hyperlink ref="M10" r:id="rId15"/>
+    <hyperlink ref="N10" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,12 +58,15 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 14:53:33</t>
+    <t>Laatst bijgewerkt: 2025-09-05 18:53:17</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>
   </si>
   <si>
+    <t>Duitsland vs Noord-Ierland</t>
+  </si>
+  <si>
     <t>Montenegro vs Tsjechië</t>
   </si>
   <si>
@@ -76,12 +79,21 @@
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
+    <t>totaal aantal schoten</t>
+  </si>
+  <si>
     <t>wedstrijd</t>
   </si>
   <si>
+    <t>duitsland</t>
+  </si>
+  <si>
     <t>montenegro</t>
   </si>
   <si>
+    <t>kylian mbappé</t>
+  </si>
+  <si>
     <t>oekraïne</t>
   </si>
   <si>
@@ -91,21 +103,33 @@
     <t>meer dan 10.5</t>
   </si>
   <si>
+    <t>meer dan 7.5</t>
+  </si>
+  <si>
+    <t>meer dan 8.5</t>
+  </si>
+  <si>
     <t>meer dan 3.5</t>
   </si>
   <si>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
+    <t>meer dan 4.5</t>
+  </si>
+  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
-    <t>meer dan 8.5</t>
-  </si>
-  <si>
     <t>meer dan 9.5</t>
   </si>
   <si>
     <t>onecasino</t>
   </si>
   <si>
+    <t>bingoal</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
@@ -115,27 +139,51 @@
     <t>minder dan 10.5</t>
   </si>
   <si>
+    <t>minder dan 7.5</t>
+  </si>
+  <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
     <t>minder dan 3.5</t>
   </si>
   <si>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
+    <t>minder dan 4.5</t>
+  </si>
+  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
-    <t>minder dan 8.5</t>
-  </si>
-  <si>
     <t>minder dan 9.5</t>
   </si>
   <si>
     <t>starcasino</t>
   </si>
   <si>
-    <t>1=58, 2=92</t>
+    <t>1=59, 2=91</t>
+  </si>
+  <si>
+    <t>1=75, 2=75</t>
+  </si>
+  <si>
+    <t>1=55, 2=95</t>
   </si>
   <si>
     <t>1=60, 2=90</t>
   </si>
   <si>
+    <t>1=96, 2=54</t>
+  </si>
+  <si>
+    <t>1=61, 2=89</t>
+  </si>
+  <si>
+    <t>1=74, 2=76</t>
+  </si>
+  <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
@@ -145,18 +193,27 @@
     <t>1=93, 2=57</t>
   </si>
   <si>
-    <t>1=74, 2=76</t>
-  </si>
-  <si>
-    <t>1=55, 2=95</t>
-  </si>
-  <si>
-    <t>€8.92</t>
+    <t>€9.25</t>
+  </si>
+  <si>
+    <t>€6.0</t>
+  </si>
+  <si>
+    <t>€5.8</t>
   </si>
   <si>
     <t>€5.46</t>
   </si>
   <si>
+    <t>€4.56</t>
+  </si>
+  <si>
+    <t>€3.73</t>
+  </si>
+  <si>
+    <t>€3.52</t>
+  </si>
+  <si>
     <t>€3.12</t>
   </si>
   <si>
@@ -169,31 +226,61 @@
     <t>€1.7</t>
   </si>
   <si>
+    <t>€1.3</t>
+  </si>
+  <si>
     <t>€1.25</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10025497</t>
   </si>
   <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168639&amp;betoffer=2549626618&amp;outcome=3856355987</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023168639#event/1023168639</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590797</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1022335870#event/1022335870</t>
+    <t>https://www.bingoal.nl/sports/#event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980</t>
+  </si>
+  <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=11998073</t>
   </si>
   <si>
+    <t>https://jacks.nl/sports/event/1023224852#event/1023224852</t>
+  </si>
+  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549442</t>
   </si>
   <si>
+    <t>https://jacks.nl/sports/event/1023224887#event/1023224887</t>
+  </si>
+  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623890</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623891</t>
+  </si>
+  <si>
+    <t>https://sports.onecasino.nl/#/event/10028349</t>
   </si>
 </sst>
 </file>
@@ -564,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -621,43 +708,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I3">
         <v>1.75</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L3">
-        <v>6.36</v>
+        <v>6.23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -665,131 +752,131 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4">
-        <v>1.7273</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="L4">
-        <v>3.64</v>
+        <v>4.3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5">
-        <v>1.4445</v>
+        <v>1.64</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L5">
-        <v>2.2</v>
+        <v>3.94</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>1.8182</v>
+        <v>1.7273</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="L6">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -797,43 +884,43 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>2.6667</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="L7">
-        <v>1.89</v>
+        <v>3.17</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -841,151 +928,473 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1.7273</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="L8">
-        <v>1.22</v>
+        <v>2.89</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="L9">
-        <v>1.22</v>
+        <v>2.65</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>3.5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10">
+        <v>1.4445</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10">
+        <v>2.2</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>2.33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11">
+        <v>1.8182</v>
+      </c>
+      <c r="J11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11">
+        <v>2.08</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>1.65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12">
+        <v>2.6667</v>
+      </c>
+      <c r="J12" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12">
+        <v>1.89</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13">
+        <v>1.64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13">
+        <v>2.6667</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13">
+        <v>1.52</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14">
+        <v>2.05</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <v>1.22</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>2.05</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15">
+        <v>1.22</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10">
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16">
+        <v>1.18</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17">
         <v>2.75</v>
       </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10">
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17">
         <v>1.6</v>
       </c>
-      <c r="J10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J17" t="s">
         <v>51</v>
       </c>
-      <c r="L10">
+      <c r="K17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17">
         <v>1.14</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>58</v>
+      <c r="M17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1" location="/event/10025497"/>
     <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="M4" r:id="rId3" location="event/1023168639"/>
-    <hyperlink ref="N4" r:id="rId4"/>
-    <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6"/>
-    <hyperlink ref="M6" r:id="rId7" location="event/1022335870"/>
+    <hyperlink ref="M4" r:id="rId3" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
+    <hyperlink ref="N4" r:id="rId4" location="event/1023224852"/>
+    <hyperlink ref="M5" r:id="rId5" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
+    <hyperlink ref="N5" r:id="rId6" location="event/1023224852"/>
+    <hyperlink ref="M6" r:id="rId7" location="event=1023168639&amp;betoffer=2549626618&amp;outcome=3856355987"/>
     <hyperlink ref="N6" r:id="rId8"/>
-    <hyperlink ref="M7" r:id="rId9" location="event/1023168639"/>
-    <hyperlink ref="N7" r:id="rId10"/>
-    <hyperlink ref="M8" r:id="rId11"/>
+    <hyperlink ref="M7" r:id="rId9" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224852"/>
+    <hyperlink ref="M8" r:id="rId11" location="event/1023168639"/>
     <hyperlink ref="N8" r:id="rId12"/>
     <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14"/>
+    <hyperlink ref="N9" r:id="rId14" location="event/1023224887"/>
     <hyperlink ref="M10" r:id="rId15"/>
     <hyperlink ref="N10" r:id="rId16"/>
+    <hyperlink ref="M11" r:id="rId17" location="event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727"/>
+    <hyperlink ref="N11" r:id="rId18"/>
+    <hyperlink ref="M12" r:id="rId19" location="event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980"/>
+    <hyperlink ref="N12" r:id="rId20"/>
+    <hyperlink ref="M13" r:id="rId21" location="event/1023168639"/>
+    <hyperlink ref="N13" r:id="rId22"/>
+    <hyperlink ref="M14" r:id="rId23"/>
+    <hyperlink ref="N14" r:id="rId24"/>
+    <hyperlink ref="M15" r:id="rId25"/>
+    <hyperlink ref="N15" r:id="rId26"/>
+    <hyperlink ref="M16" r:id="rId27"/>
+    <hyperlink ref="N16" r:id="rId28" location="/event/10028349"/>
+    <hyperlink ref="M17" r:id="rId29"/>
+    <hyperlink ref="N17" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 18:53:17</t>
+    <t>Laatst bijgewerkt: 2025-09-05 18:56:02</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>
@@ -70,18 +70,12 @@
     <t>Montenegro vs Tsjechië</t>
   </si>
   <si>
-    <t>Oekraïne vs Frankrijk</t>
-  </si>
-  <si>
     <t>IJsland vs Azerbeidzjan</t>
   </si>
   <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
-    <t>totaal aantal schoten</t>
-  </si>
-  <si>
     <t>wedstrijd</t>
   </si>
   <si>
@@ -91,12 +85,6 @@
     <t>montenegro</t>
   </si>
   <si>
-    <t>kylian mbappé</t>
-  </si>
-  <si>
-    <t>oekraïne</t>
-  </si>
-  <si>
     <t>azerbeidzjan</t>
   </si>
   <si>
@@ -115,15 +103,9 @@
     <t>meer dan 6.5</t>
   </si>
   <si>
-    <t>meer dan 4.5</t>
-  </si>
-  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
-    <t>meer dan 9.5</t>
-  </si>
-  <si>
     <t>onecasino</t>
   </si>
   <si>
@@ -151,18 +133,15 @@
     <t>minder dan 6.5</t>
   </si>
   <si>
-    <t>minder dan 4.5</t>
-  </si>
-  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
-    <t>minder dan 9.5</t>
-  </si>
-  <si>
     <t>starcasino</t>
   </si>
   <si>
+    <t>betmgm</t>
+  </si>
+  <si>
     <t>1=59, 2=91</t>
   </si>
   <si>
@@ -181,12 +160,6 @@
     <t>1=61, 2=89</t>
   </si>
   <si>
-    <t>1=74, 2=76</t>
-  </si>
-  <si>
-    <t>1=44, 2=106</t>
-  </si>
-  <si>
     <t>1=66, 2=84</t>
   </si>
   <si>
@@ -211,27 +184,15 @@
     <t>€3.73</t>
   </si>
   <si>
-    <t>€3.52</t>
-  </si>
-  <si>
-    <t>€3.12</t>
-  </si>
-  <si>
     <t>€2.73</t>
   </si>
   <si>
     <t>€2.0</t>
   </si>
   <si>
-    <t>€1.7</t>
-  </si>
-  <si>
     <t>€1.3</t>
   </si>
   <si>
-    <t>€1.25</t>
-  </si>
-  <si>
     <t>https://sports.onecasino.nl/#/event/10025497</t>
   </si>
   <si>
@@ -250,9 +211,6 @@
     <t>https://jacks.nl/sports/event/1023168639#event/1023168639</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8590797</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727</t>
   </si>
   <si>
@@ -271,16 +229,10 @@
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549442</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1023224887#event/1023224887</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623890</t>
-  </si>
-  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623891</t>
   </si>
   <si>
-    <t>https://sports.onecasino.nl/#/event/10028349</t>
+    <t>https://www.betmgm.nl/betting/sports/event/1023224852?coupon=single%7C3865636663%7C1.70%7Creplace</t>
   </si>
 </sst>
 </file>
@@ -651,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -708,43 +660,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>2.73</v>
       </c>
       <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
         <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>48</v>
       </c>
       <c r="I3">
         <v>1.75</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L3">
         <v>6.23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -752,43 +704,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>2.1</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>2.08</v>
       </c>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L4">
         <v>4.3</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -796,43 +748,43 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>2.85</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I5">
         <v>1.64</v>
       </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L5">
         <v>3.94</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -840,43 +792,43 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
       </c>
       <c r="F6">
         <v>2.6</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>1.7273</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L6">
         <v>3.64</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -884,43 +836,43 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>1.61</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>2.88</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L7">
         <v>3.17</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -928,43 +880,43 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>2.55</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I8">
         <v>1.7273</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="L8">
         <v>2.89</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -972,395 +924,175 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>2.02</v>
+        <v>1.8182</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9">
+        <v>2.08</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L9">
-        <v>2.65</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="N9" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10">
+        <v>1.65</v>
+      </c>
+      <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="F10">
-        <v>3.5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I10">
-        <v>1.4445</v>
+        <v>2.6667</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>1.89</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L10">
-        <v>2.2</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I11">
-        <v>1.8182</v>
+        <v>2.6667</v>
       </c>
       <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
         <v>57</v>
       </c>
-      <c r="K11" t="s">
-        <v>67</v>
-      </c>
       <c r="L11">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>2.5</v>
+      </c>
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12">
-        <v>1.65</v>
-      </c>
-      <c r="G12" t="s">
-        <v>46</v>
-      </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I12">
-        <v>2.6667</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" t="s">
         <v>58</v>
       </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
       <c r="L12">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13">
-        <v>1.64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13">
-        <v>2.6667</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13">
-        <v>1.52</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14">
-        <v>2.05</v>
-      </c>
-      <c r="G14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K14" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14">
-        <v>1.22</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15">
-        <v>2.05</v>
-      </c>
-      <c r="G15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="J15" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15">
-        <v>1.22</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16">
-        <v>2.5</v>
-      </c>
-      <c r="G16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="s">
-        <v>54</v>
-      </c>
-      <c r="K16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16">
-        <v>1.18</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17">
-        <v>2.75</v>
-      </c>
-      <c r="G17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17">
-        <v>1.6</v>
-      </c>
-      <c r="J17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17">
-        <v>1.14</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1377,24 +1109,14 @@
     <hyperlink ref="N7" r:id="rId10" location="event/1023224852"/>
     <hyperlink ref="M8" r:id="rId11" location="event/1023168639"/>
     <hyperlink ref="N8" r:id="rId12"/>
-    <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14" location="event/1023224887"/>
-    <hyperlink ref="M10" r:id="rId15"/>
+    <hyperlink ref="M9" r:id="rId13" location="event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727"/>
+    <hyperlink ref="N9" r:id="rId14"/>
+    <hyperlink ref="M10" r:id="rId15" location="event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980"/>
     <hyperlink ref="N10" r:id="rId16"/>
-    <hyperlink ref="M11" r:id="rId17" location="event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727"/>
+    <hyperlink ref="M11" r:id="rId17" location="event/1023168639"/>
     <hyperlink ref="N11" r:id="rId18"/>
-    <hyperlink ref="M12" r:id="rId19" location="event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980"/>
+    <hyperlink ref="M12" r:id="rId19"/>
     <hyperlink ref="N12" r:id="rId20"/>
-    <hyperlink ref="M13" r:id="rId21" location="event/1023168639"/>
-    <hyperlink ref="N13" r:id="rId22"/>
-    <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24"/>
-    <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26"/>
-    <hyperlink ref="M16" r:id="rId27"/>
-    <hyperlink ref="N16" r:id="rId28" location="/event/10028349"/>
-    <hyperlink ref="M17" r:id="rId29"/>
-    <hyperlink ref="N17" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 18:56:02</t>
+    <t>Laatst bijgewerkt: 2025-09-05 18:56:35</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 18:56:35</t>
+    <t>Laatst bijgewerkt: 2025-09-05 18:58:36</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 18:58:36</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:00:37</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:00:37</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:02:38</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:02:38</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:04:40</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:04:40</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:06:41</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:06:41</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:08:43</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:08:43</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:10:44</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:10:44</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:12:45</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:12:45</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:14:47</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:14:47</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:16:48</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:16:48</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:18:50</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:18:50</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:20:51</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:20:51</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:22:52</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:22:52</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:24:53</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:24:53</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:26:55</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:26:55</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:28:56</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:28:56</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:30:57</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:30:57</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:32:59</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:32:59</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:35:00</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:35:00</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:37:01</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:37:01</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:39:03</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:39:03</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:41:04</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:41:04</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:43:05</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:43:05</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:45:06</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:45:06</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:47:07</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:47:07</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:49:09</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:49:09</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:51:10</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:51:10</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:53:11</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:53:11</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:55:12</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:55:12</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:57:14</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:57:14</t>
+    <t>Laatst bijgewerkt: 2025-09-05 19:59:15</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 19:59:15</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:01:16</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:01:16</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:03:17</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:03:17</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:05:19</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:05:19</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:07:20</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:07:20</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:09:21</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:09:21</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:11:23</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:11:23</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:13:24</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:13:24</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:15:25</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:15:25</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:17:26</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:17:26</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:19:28</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:19:28</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:21:29</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:21:29</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:23:30</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:23:30</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:25:32</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:25:32</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:27:33</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:27:33</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:29:35</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:29:35</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:31:36</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:31:36</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:33:37</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:33:37</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:35:38</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:35:38</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:37:40</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:37:40</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:39:41</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:39:41</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:41:42</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:41:42</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:43:43</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:43:43</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:45:45</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:45:45</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:47:46</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:47:46</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:49:47</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:49:47</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:51:48</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:51:48</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:53:50</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:53:50</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:55:51</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:55:51</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:57:52</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:57:52</t>
+    <t>Laatst bijgewerkt: 2025-09-05 20:59:53</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 20:59:53</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:01:55</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:01:55</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:03:56</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:03:56</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:05:57</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:05:57</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:07:58</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:07:58</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:10:00</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:10:00</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:12:01</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:12:01</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:14:03</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:14:03</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:16:04</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:16:04</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:18:05</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:18:05</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:20:06</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:20:06</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:22:08</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:22:08</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:24:09</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:24:09</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:26:11</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:26:11</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:28:12</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:28:12</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:30:13</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:30:13</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:32:14</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:32:14</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:34:16</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:34:16</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:36:17</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:36:17</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:38:19</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:38:19</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:40:20</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:40:20</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:42:21</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:42:21</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:44:22</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:44:22</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:46:24</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:46:24</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:48:25</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:48:25</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:50:26</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:50:26</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:52:27</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:52:27</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:54:29</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:54:29</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:56:30</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:56:30</t>
+    <t>Laatst bijgewerkt: 2025-09-05 21:58:31</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 21:58:31</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:00:32</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:00:32</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:02:34</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:02:34</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:04:35</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:04:35</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:06:36</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:06:36</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:08:37</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:08:37</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:10:39</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:10:39</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:12:40</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:12:40</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:14:41</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:14:41</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:16:43</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:16:43</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:18:45</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:18:45</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:20:47</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:20:47</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:22:48</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:22:48</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:24:49</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:24:49</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:26:50</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:26:50</t>
+    <t>Laatst bijgewerkt: 2025-09-05 22:28:52</t>
   </si>
   <si>
     <t>Chicago Fire vs New England Revolution</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,181 +58,466 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-05 22:28:52</t>
-  </si>
-  <si>
-    <t>Chicago Fire vs New England Revolution</t>
+    <t>Laatst bijgewerkt: 2025-09-06 16:57:47</t>
+  </si>
+  <si>
+    <t>Armenië vs Portugal</t>
+  </si>
+  <si>
+    <t>Bolivia vs Brazilië</t>
+  </si>
+  <si>
+    <t>Litouwen vs Nederland</t>
   </si>
   <si>
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
-    <t>Montenegro vs Tsjechië</t>
-  </si>
-  <si>
-    <t>IJsland vs Azerbeidzjan</t>
+    <t>Turkije vs Spanje</t>
+  </si>
+  <si>
+    <t>Engeland vs Andorra</t>
+  </si>
+  <si>
+    <t>totaal aantal schoten</t>
   </si>
   <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
+    <t>portugal</t>
+  </si>
+  <si>
     <t>wedstrijd</t>
   </si>
   <si>
+    <t>sem steijn</t>
+  </si>
+  <si>
+    <t>spanje</t>
+  </si>
+  <si>
     <t>duitsland</t>
   </si>
   <si>
-    <t>montenegro</t>
-  </si>
-  <si>
-    <t>azerbeidzjan</t>
+    <t>nederland</t>
+  </si>
+  <si>
+    <t>armenië</t>
+  </si>
+  <si>
+    <t>engeland</t>
+  </si>
+  <si>
+    <t>brazilië</t>
+  </si>
+  <si>
+    <t>meer dan 19.5</t>
+  </si>
+  <si>
+    <t>meer dan 17.5</t>
+  </si>
+  <si>
+    <t>meer dan 20.5</t>
+  </si>
+  <si>
+    <t>meer dan 18.5</t>
+  </si>
+  <si>
+    <t>meer dan 8.5</t>
+  </si>
+  <si>
+    <t>meer dan 16.5</t>
+  </si>
+  <si>
+    <t>meer dan 4.5</t>
+  </si>
+  <si>
+    <t>meer dan 7.5</t>
   </si>
   <si>
     <t>meer dan 10.5</t>
   </si>
   <si>
-    <t>meer dan 7.5</t>
-  </si>
-  <si>
-    <t>meer dan 8.5</t>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
+    <t>meer dan 5.5</t>
   </si>
   <si>
     <t>meer dan 3.5</t>
   </si>
   <si>
-    <t>meer dan 6.5</t>
-  </si>
-  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
+    <t>meer dan 22.5</t>
+  </si>
+  <si>
+    <t>meer dan 24.5</t>
+  </si>
+  <si>
+    <t>bingoal</t>
+  </si>
+  <si>
     <t>onecasino</t>
   </si>
   <si>
-    <t>bingoal</t>
+    <t>vbet</t>
+  </si>
+  <si>
+    <t>toto</t>
   </si>
   <si>
     <t>jacks</t>
   </si>
   <si>
-    <t>toto</t>
+    <t>minder dan 19.5</t>
+  </si>
+  <si>
+    <t>minder dan 17.5</t>
+  </si>
+  <si>
+    <t>minder dan 20.5</t>
+  </si>
+  <si>
+    <t>minder dan 18.5</t>
+  </si>
+  <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
+    <t>minder dan 16.5</t>
+  </si>
+  <si>
+    <t>minder dan 4.5</t>
+  </si>
+  <si>
+    <t>minder dan 7.5</t>
   </si>
   <si>
     <t>minder dan 10.5</t>
   </si>
   <si>
-    <t>minder dan 7.5</t>
-  </si>
-  <si>
-    <t>minder dan 8.5</t>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
+    <t>minder dan 5.5</t>
   </si>
   <si>
     <t>minder dan 3.5</t>
   </si>
   <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
+    <t>minder dan 9.5</t>
+  </si>
+  <si>
+    <t>minder dan 22.5</t>
+  </si>
+  <si>
+    <t>minder dan 24.5</t>
+  </si>
+  <si>
+    <t>kambi</t>
+  </si>
+  <si>
     <t>starcasino</t>
   </si>
   <si>
-    <t>betmgm</t>
-  </si>
-  <si>
-    <t>1=59, 2=91</t>
+    <t>1=76, 2=74</t>
   </si>
   <si>
     <t>1=75, 2=75</t>
   </si>
   <si>
-    <t>1=55, 2=95</t>
-  </si>
-  <si>
-    <t>1=60, 2=90</t>
-  </si>
-  <si>
-    <t>1=96, 2=54</t>
+    <t>1=100, 2=50</t>
+  </si>
+  <si>
+    <t>1=74, 2=76</t>
+  </si>
+  <si>
+    <t>1=66, 2=84</t>
+  </si>
+  <si>
+    <t>1=99, 2=51</t>
+  </si>
+  <si>
+    <t>1=90, 2=60</t>
+  </si>
+  <si>
+    <t>1=65, 2=85</t>
+  </si>
+  <si>
+    <t>1=89, 2=61</t>
+  </si>
+  <si>
+    <t>1=73, 2=77</t>
+  </si>
+  <si>
+    <t>1=111, 2=39</t>
+  </si>
+  <si>
+    <t>1=52, 2=98</t>
+  </si>
+  <si>
+    <t>1=110, 2=40</t>
+  </si>
+  <si>
+    <t>1=93, 2=57</t>
+  </si>
+  <si>
+    <t>1=62, 2=88</t>
+  </si>
+  <si>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
+    <t>1=58, 2=92</t>
+  </si>
+  <si>
+    <t>1=84, 2=66</t>
+  </si>
+  <si>
+    <t>1=53, 2=97</t>
   </si>
   <si>
     <t>1=61, 2=89</t>
   </si>
   <si>
-    <t>1=66, 2=84</t>
-  </si>
-  <si>
-    <t>1=93, 2=57</t>
-  </si>
-  <si>
-    <t>€9.25</t>
+    <t>1=95, 2=55</t>
+  </si>
+  <si>
+    <t>1=44, 2=106</t>
+  </si>
+  <si>
+    <t>1=15, 2=135</t>
+  </si>
+  <si>
+    <t>1=82, 2=68</t>
+  </si>
+  <si>
+    <t>1=112, 2=38</t>
+  </si>
+  <si>
+    <t>1=78, 2=72</t>
+  </si>
+  <si>
+    <t>1=54, 2=96</t>
+  </si>
+  <si>
+    <t>€16.5</t>
+  </si>
+  <si>
+    <t>€15.0</t>
+  </si>
+  <si>
+    <t>€14.0</t>
+  </si>
+  <si>
+    <t>€12.8</t>
+  </si>
+  <si>
+    <t>€12.12</t>
+  </si>
+  <si>
+    <t>€12.36</t>
+  </si>
+  <si>
+    <t>€12.0</t>
+  </si>
+  <si>
+    <t>€11.2</t>
+  </si>
+  <si>
+    <t>€10.43</t>
+  </si>
+  <si>
+    <t>€8.62</t>
+  </si>
+  <si>
+    <t>€7.62</t>
   </si>
   <si>
     <t>€6.0</t>
   </si>
   <si>
-    <t>€5.8</t>
-  </si>
-  <si>
-    <t>€5.46</t>
-  </si>
-  <si>
-    <t>€4.56</t>
-  </si>
-  <si>
-    <t>€3.73</t>
-  </si>
-  <si>
-    <t>€2.73</t>
+    <t>€6.2</t>
+  </si>
+  <si>
+    <t>€5.31</t>
+  </si>
+  <si>
+    <t>€4.88</t>
+  </si>
+  <si>
+    <t>€4.7</t>
+  </si>
+  <si>
+    <t>€3.87</t>
+  </si>
+  <si>
+    <t>€3.3</t>
+  </si>
+  <si>
+    <t>€1.9</t>
+  </si>
+  <si>
+    <t>€1.8</t>
+  </si>
+  <si>
+    <t>€2.04</t>
+  </si>
+  <si>
+    <t>€1.05</t>
+  </si>
+  <si>
+    <t>€2.19</t>
+  </si>
+  <si>
+    <t>€1.25</t>
+  </si>
+  <si>
+    <t>€1.58</t>
+  </si>
+  <si>
+    <t>€0.0</t>
+  </si>
+  <si>
+    <t>€1.7</t>
+  </si>
+  <si>
+    <t>€1.5</t>
   </si>
   <si>
     <t>€2.0</t>
   </si>
   <si>
+    <t>€1.32</t>
+  </si>
+  <si>
     <t>€1.3</t>
   </si>
   <si>
-    <t>https://sports.onecasino.nl/#/event/10025497</t>
+    <t>€1.2</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639875&amp;outcome=3856344538</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504</t>
+  </si>
+  <si>
+    <t>https://sports.onecasino.nl/#/event/10035960</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487</t>
+  </si>
+  <si>
+    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
+  </si>
+  <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298</t>
   </si>
   <si>
     <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359</t>
   </si>
   <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060</t>
+  </si>
+  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023168639&amp;betoffer=2549626618&amp;outcome=3856355987</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1023168639#event/1023168639</t>
-  </si>
-  <si>
-    <t>https://www.bingoal.nl/sports/#event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727</t>
-  </si>
-  <si>
-    <t>https://www.bingoal.nl/sports/#event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980</t>
-  </si>
-  <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=11998073</t>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621</t>
+  </si>
+  <si>
+    <t>https://jacks.nl/sports/event/1024296378#event/1024296378</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344568%7C2.25%7Creplace</t>
+  </si>
+  <si>
+    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344699%7C3.30%7Creplace</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12631456</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3864494198%7C1.93%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344639%7C2.70%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865660847%7C2.06%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344605%7C4.10%7Creplace</t>
+  </si>
+  <si>
+    <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865649377%7C2.75%7Creplace</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642398</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224852#event/1023224852</t>
   </si>
   <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549442</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12623891</t>
-  </si>
-  <si>
-    <t>https://www.betmgm.nl/betting/sports/event/1023224852?coupon=single%7C3865636663%7C1.70%7Creplace</t>
+    <t>https://jacks.nl/sports/event/1023224902#event/1023224902</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023168666?coupon=single%7C3862503622%7C2.02%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865661081%7C4.00%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833</t>
+  </si>
+  <si>
+    <t>https://sports.onecasino.nl/#/event/10028349</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549445</t>
   </si>
 </sst>
 </file>
@@ -603,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -660,463 +945,1567 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="I3">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="L3">
-        <v>6.23</v>
+        <v>10.1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I4">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>4.3</v>
+        <v>9.09</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F5">
-        <v>2.85</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I5">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="L5">
-        <v>3.94</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F6">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I6">
-        <v>1.7273</v>
+        <v>2.1667</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="L6">
-        <v>3.64</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>1.61</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I7">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="L7">
-        <v>3.17</v>
+        <v>7.86</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I8">
-        <v>1.7273</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="L8">
-        <v>2.89</v>
+        <v>7.77</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F9">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="I9">
-        <v>1.8182</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="L9">
-        <v>2.08</v>
+        <v>7.71</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I10">
-        <v>2.6667</v>
+        <v>1.9091</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="L10">
-        <v>1.89</v>
+        <v>7.3</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F11">
-        <v>1.64</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I11">
-        <v>2.6667</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="K11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>7.05</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12">
+        <v>1.81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12">
+        <v>2.63</v>
+      </c>
+      <c r="J12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12">
+        <v>6.73</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13">
+        <v>2.19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13">
+        <v>2.06</v>
+      </c>
+      <c r="J13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13">
+        <v>5.79</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>1.42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14">
+        <v>4.1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14">
+        <v>5.19</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15">
+        <v>1.61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15">
+        <v>4.55</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16">
+        <v>1.42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16">
+        <v>3.95</v>
+      </c>
+      <c r="J16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16">
+        <v>4.26</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17">
+        <v>1.67</v>
+      </c>
+      <c r="G17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17">
+        <v>2.75</v>
+      </c>
+      <c r="J17" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17">
+        <v>3.76</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18">
+        <v>2.5</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18">
+        <v>1.76</v>
+      </c>
+      <c r="J18" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18">
+        <v>3.18</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <v>2.5</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19">
+        <v>1.76</v>
+      </c>
+      <c r="J19" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" t="s">
+        <v>113</v>
+      </c>
+      <c r="L19">
+        <v>3.18</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>86</v>
+      </c>
+      <c r="K20" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20">
+        <v>3.08</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>1.91</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21">
+        <v>2.23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" t="s">
+        <v>115</v>
+      </c>
+      <c r="L21">
+        <v>2.8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22">
+        <v>2.1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" t="s">
+        <v>116</v>
+      </c>
+      <c r="L22">
+        <v>2.38</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23">
+        <v>2.45</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23">
+        <v>1.74</v>
+      </c>
+      <c r="J23" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L23">
+        <v>1.71</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24">
+        <v>2.65</v>
+      </c>
+      <c r="G24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24">
+        <v>1.65</v>
+      </c>
+      <c r="J24" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24">
+        <v>1.66</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25">
+        <v>1.81</v>
+      </c>
+      <c r="G25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25">
+        <v>2.32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" t="s">
+        <v>119</v>
+      </c>
+      <c r="L25">
+        <v>1.65</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26">
+        <v>2.85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26">
+        <v>1.58</v>
+      </c>
+      <c r="J26" t="s">
+        <v>90</v>
+      </c>
+      <c r="K26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L26">
+        <v>1.62</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27">
+        <v>2.5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27">
+        <v>1.71</v>
+      </c>
+      <c r="J27" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" t="s">
+        <v>121</v>
+      </c>
+      <c r="L27">
+        <v>1.52</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28">
+        <v>1.61</v>
+      </c>
+      <c r="G28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28">
+        <v>2.75</v>
+      </c>
+      <c r="J28" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" t="s">
+        <v>122</v>
+      </c>
+      <c r="L28">
+        <v>1.52</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29">
+        <v>3.5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29">
+        <v>1.43</v>
+      </c>
+      <c r="J29" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29">
+        <v>1.5</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30">
+        <v>1.13</v>
+      </c>
+      <c r="J30" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" t="s">
+        <v>124</v>
+      </c>
+      <c r="L30">
+        <v>1.5</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31">
+        <v>1.85</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31">
+        <v>2.25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" t="s">
+        <v>125</v>
+      </c>
+      <c r="L31">
+        <v>1.5</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32">
+        <v>2.04</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32">
+        <v>2.02</v>
+      </c>
+      <c r="J32" t="s">
+        <v>72</v>
+      </c>
+      <c r="K32" t="s">
+        <v>126</v>
+      </c>
+      <c r="L32">
+        <v>1.48</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>24</v>
       </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12">
+      <c r="D33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33">
+        <v>1.36</v>
+      </c>
+      <c r="G33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33" t="s">
+        <v>96</v>
+      </c>
+      <c r="K33" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33">
+        <v>1.47</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34">
+        <v>1.94</v>
+      </c>
+      <c r="G34" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34">
+        <v>2.12</v>
+      </c>
+      <c r="J34" t="s">
+        <v>97</v>
+      </c>
+      <c r="K34" t="s">
+        <v>128</v>
+      </c>
+      <c r="L34">
+        <v>1.28</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35">
         <v>2.5</v>
       </c>
-      <c r="G12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12">
+      <c r="G35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I35">
         <v>1.7</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J35" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35" t="s">
+        <v>129</v>
+      </c>
+      <c r="L35">
+        <v>1.18</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
         <v>47</v>
       </c>
-      <c r="K12" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12">
-        <v>1.18</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>72</v>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36">
+        <v>2.8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I36">
+        <v>1.5834</v>
+      </c>
+      <c r="J36" t="s">
+        <v>98</v>
+      </c>
+      <c r="K36" t="s">
+        <v>130</v>
+      </c>
+      <c r="L36">
+        <v>1.13</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M3" r:id="rId1" location="/event/10025497"/>
+    <hyperlink ref="M3" r:id="rId1" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
     <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="M4" r:id="rId3" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
-    <hyperlink ref="N4" r:id="rId4" location="event/1023224852"/>
-    <hyperlink ref="M5" r:id="rId5" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
-    <hyperlink ref="N5" r:id="rId6" location="event/1023224852"/>
-    <hyperlink ref="M6" r:id="rId7" location="event=1023168639&amp;betoffer=2549626618&amp;outcome=3856355987"/>
+    <hyperlink ref="M4" r:id="rId3" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
+    <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
+    <hyperlink ref="M5" r:id="rId5" location="event=1023224918&amp;betoffer=2549639875&amp;outcome=3856344538"/>
+    <hyperlink ref="N5" r:id="rId6"/>
+    <hyperlink ref="M6" r:id="rId7" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
     <hyperlink ref="N6" r:id="rId8"/>
-    <hyperlink ref="M7" r:id="rId9" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
-    <hyperlink ref="N7" r:id="rId10" location="event/1023224852"/>
-    <hyperlink ref="M8" r:id="rId11" location="event/1023168639"/>
-    <hyperlink ref="N8" r:id="rId12"/>
-    <hyperlink ref="M9" r:id="rId13" location="event=1022335870&amp;betoffer=2549614664&amp;outcome=3856406727"/>
+    <hyperlink ref="M7" r:id="rId9" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
+    <hyperlink ref="N7" r:id="rId10"/>
+    <hyperlink ref="M8" r:id="rId11" location="event=1023224918&amp;betoffer=2549639875&amp;outcome=3856344538"/>
+    <hyperlink ref="N8" r:id="rId12" location="event/1023224918"/>
+    <hyperlink ref="M9" r:id="rId13" location="event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504"/>
     <hyperlink ref="N9" r:id="rId14"/>
-    <hyperlink ref="M10" r:id="rId15" location="event=1023168639&amp;betoffer=2549626614&amp;outcome=3856355980"/>
+    <hyperlink ref="M10" r:id="rId15" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
     <hyperlink ref="N10" r:id="rId16"/>
-    <hyperlink ref="M11" r:id="rId17" location="event/1023168639"/>
-    <hyperlink ref="N11" r:id="rId18"/>
-    <hyperlink ref="M12" r:id="rId19"/>
-    <hyperlink ref="N12" r:id="rId20"/>
+    <hyperlink ref="M11" r:id="rId17" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
+    <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
+    <hyperlink ref="M12" r:id="rId19" location="event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504"/>
+    <hyperlink ref="N12" r:id="rId20" location="event/1023224918"/>
+    <hyperlink ref="M13" r:id="rId21" location="/event/10035960"/>
+    <hyperlink ref="N13" r:id="rId22"/>
+    <hyperlink ref="M14" r:id="rId23" location="event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487"/>
+    <hyperlink ref="N14" r:id="rId24"/>
+    <hyperlink ref="M15" r:id="rId25"/>
+    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
+    <hyperlink ref="M16" r:id="rId27" location="event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487"/>
+    <hyperlink ref="N16" r:id="rId28" location="event/1023224918"/>
+    <hyperlink ref="M17" r:id="rId29" location="/event/10035960"/>
+    <hyperlink ref="N17" r:id="rId30"/>
+    <hyperlink ref="M18" r:id="rId31"/>
+    <hyperlink ref="N18" r:id="rId32"/>
+    <hyperlink ref="M19" r:id="rId33" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
+    <hyperlink ref="N19" r:id="rId34"/>
+    <hyperlink ref="M20" r:id="rId35"/>
+    <hyperlink ref="N20" r:id="rId36" location="event/1023224945"/>
+    <hyperlink ref="M21" r:id="rId37"/>
+    <hyperlink ref="N21" r:id="rId38" location="event/1023224945"/>
+    <hyperlink ref="M22" r:id="rId39" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
+    <hyperlink ref="N22" r:id="rId40" location="event/1023224852"/>
+    <hyperlink ref="M23" r:id="rId41"/>
+    <hyperlink ref="N23" r:id="rId42" location="event/1023224945"/>
+    <hyperlink ref="M24" r:id="rId43" location="event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662"/>
+    <hyperlink ref="N24" r:id="rId44" location="event/1023224918"/>
+    <hyperlink ref="M25" r:id="rId45" location="event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060"/>
+    <hyperlink ref="N25" r:id="rId46" location="event/1023224902"/>
+    <hyperlink ref="M26" r:id="rId47" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
+    <hyperlink ref="N26" r:id="rId48" location="event/1023224852"/>
+    <hyperlink ref="M27" r:id="rId49" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
+    <hyperlink ref="N27" r:id="rId50" location="event/1023224902"/>
+    <hyperlink ref="M28" r:id="rId51" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
+    <hyperlink ref="N28" r:id="rId52" location="event/1023224852"/>
+    <hyperlink ref="M29" r:id="rId53"/>
+    <hyperlink ref="N29" r:id="rId54" location="event/1023224945"/>
+    <hyperlink ref="M30" r:id="rId55"/>
+    <hyperlink ref="N30" r:id="rId56" location="event/1023224945"/>
+    <hyperlink ref="M31" r:id="rId57"/>
+    <hyperlink ref="N31" r:id="rId58" location="event/1023224945"/>
+    <hyperlink ref="M32" r:id="rId59" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
+    <hyperlink ref="N32" r:id="rId60"/>
+    <hyperlink ref="M33" r:id="rId61" location="/event/10035960"/>
+    <hyperlink ref="N33" r:id="rId62"/>
+    <hyperlink ref="M34" r:id="rId63" location="event/1024296378"/>
+    <hyperlink ref="N34" r:id="rId64" location="event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833"/>
+    <hyperlink ref="M35" r:id="rId65"/>
+    <hyperlink ref="N35" r:id="rId66" location="/event/10028349"/>
+    <hyperlink ref="M36" r:id="rId67" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
+    <hyperlink ref="N36" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="189">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 16:57:47</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:03:24</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -70,12 +70,12 @@
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
+    <t>Turkije vs Spanje</t>
+  </si>
+  <si>
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
-    <t>Turkije vs Spanje</t>
-  </si>
-  <si>
     <t>Engeland vs Andorra</t>
   </si>
   <si>
@@ -94,21 +94,21 @@
     <t>sem steijn</t>
   </si>
   <si>
+    <t>armenië</t>
+  </si>
+  <si>
     <t>spanje</t>
   </si>
   <si>
+    <t>engeland</t>
+  </si>
+  <si>
     <t>duitsland</t>
   </si>
   <si>
     <t>nederland</t>
   </si>
   <si>
-    <t>armenië</t>
-  </si>
-  <si>
-    <t>engeland</t>
-  </si>
-  <si>
     <t>brazilië</t>
   </si>
   <si>
@@ -136,30 +136,39 @@
     <t>meer dan 7.5</t>
   </si>
   <si>
+    <t>meer dan 2.5</t>
+  </si>
+  <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
     <t>meer dan 10.5</t>
   </si>
   <si>
-    <t>meer dan 6.5</t>
-  </si>
-  <si>
     <t>meer dan 5.5</t>
   </si>
   <si>
     <t>meer dan 3.5</t>
   </si>
   <si>
-    <t>meer dan 2.5</t>
-  </si>
-  <si>
-    <t>meer dan 9.5</t>
-  </si>
-  <si>
     <t>meer dan 22.5</t>
   </si>
   <si>
+    <t>meer dan 23.5</t>
+  </si>
+  <si>
+    <t>meer dan 21.5</t>
+  </si>
+  <si>
     <t>meer dan 24.5</t>
   </si>
   <si>
+    <t>meer dan 1.5</t>
+  </si>
+  <si>
     <t>bingoal</t>
   </si>
   <si>
@@ -199,30 +208,39 @@
     <t>minder dan 7.5</t>
   </si>
   <si>
+    <t>minder dan 2.5</t>
+  </si>
+  <si>
+    <t>minder dan 9.5</t>
+  </si>
+  <si>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
     <t>minder dan 10.5</t>
   </si>
   <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
     <t>minder dan 5.5</t>
   </si>
   <si>
     <t>minder dan 3.5</t>
   </si>
   <si>
-    <t>minder dan 2.5</t>
-  </si>
-  <si>
-    <t>minder dan 9.5</t>
-  </si>
-  <si>
     <t>minder dan 22.5</t>
   </si>
   <si>
+    <t>minder dan 23.5</t>
+  </si>
+  <si>
+    <t>minder dan 21.5</t>
+  </si>
+  <si>
     <t>minder dan 24.5</t>
   </si>
   <si>
+    <t>minder dan 1.5</t>
+  </si>
+  <si>
     <t>kambi</t>
   </si>
   <si>
@@ -232,55 +250,67 @@
     <t>1=76, 2=74</t>
   </si>
   <si>
+    <t>1=100, 2=50</t>
+  </si>
+  <si>
+    <t>1=74, 2=76</t>
+  </si>
+  <si>
+    <t>1=66, 2=84</t>
+  </si>
+  <si>
+    <t>1=99, 2=51</t>
+  </si>
+  <si>
+    <t>1=90, 2=60</t>
+  </si>
+  <si>
+    <t>1=65, 2=85</t>
+  </si>
+  <si>
+    <t>1=89, 2=61</t>
+  </si>
+  <si>
+    <t>1=73, 2=77</t>
+  </si>
+  <si>
+    <t>1=111, 2=39</t>
+  </si>
+  <si>
+    <t>1=52, 2=98</t>
+  </si>
+  <si>
+    <t>1=110, 2=40</t>
+  </si>
+  <si>
+    <t>1=93, 2=57</t>
+  </si>
+  <si>
+    <t>1=59, 2=91</t>
+  </si>
+  <si>
+    <t>1=61, 2=89</t>
+  </si>
+  <si>
+    <t>1=62, 2=88</t>
+  </si>
+  <si>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
     <t>1=75, 2=75</t>
   </si>
   <si>
-    <t>1=100, 2=50</t>
-  </si>
-  <si>
-    <t>1=74, 2=76</t>
-  </si>
-  <si>
-    <t>1=66, 2=84</t>
-  </si>
-  <si>
-    <t>1=99, 2=51</t>
-  </si>
-  <si>
-    <t>1=90, 2=60</t>
-  </si>
-  <si>
-    <t>1=65, 2=85</t>
-  </si>
-  <si>
-    <t>1=89, 2=61</t>
-  </si>
-  <si>
-    <t>1=73, 2=77</t>
-  </si>
-  <si>
-    <t>1=111, 2=39</t>
-  </si>
-  <si>
-    <t>1=52, 2=98</t>
-  </si>
-  <si>
-    <t>1=110, 2=40</t>
-  </si>
-  <si>
-    <t>1=93, 2=57</t>
-  </si>
-  <si>
-    <t>1=62, 2=88</t>
-  </si>
-  <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
-    <t>1=58, 2=92</t>
+    <t>1=54, 2=96</t>
+  </si>
+  <si>
+    <t>1=86, 2=64</t>
+  </si>
+  <si>
+    <t>1=55, 2=95</t>
   </si>
   <si>
     <t>1=84, 2=66</t>
@@ -289,15 +319,12 @@
     <t>1=53, 2=97</t>
   </si>
   <si>
-    <t>1=61, 2=89</t>
+    <t>1=44, 2=106</t>
   </si>
   <si>
     <t>1=95, 2=55</t>
   </si>
   <si>
-    <t>1=44, 2=106</t>
-  </si>
-  <si>
     <t>1=15, 2=135</t>
   </si>
   <si>
@@ -307,16 +334,16 @@
     <t>1=112, 2=38</t>
   </si>
   <si>
+    <t>1=98, 2=52</t>
+  </si>
+  <si>
     <t>1=78, 2=72</t>
   </si>
   <si>
-    <t>1=54, 2=96</t>
-  </si>
-  <si>
     <t>€16.5</t>
   </si>
   <si>
-    <t>€15.0</t>
+    <t>€15.02</t>
   </si>
   <si>
     <t>€14.0</t>
@@ -337,7 +364,7 @@
     <t>€11.2</t>
   </si>
   <si>
-    <t>€10.43</t>
+    <t>€11.09</t>
   </si>
   <si>
     <t>€8.62</t>
@@ -355,49 +382,67 @@
     <t>€5.31</t>
   </si>
   <si>
+    <t>€4.7</t>
+  </si>
+  <si>
+    <t>€4.86</t>
+  </si>
+  <si>
     <t>€4.88</t>
   </si>
   <si>
-    <t>€4.7</t>
-  </si>
-  <si>
     <t>€3.87</t>
   </si>
   <si>
+    <t>€3.0</t>
+  </si>
+  <si>
+    <t>€3.6</t>
+  </si>
+  <si>
     <t>€3.3</t>
   </si>
   <si>
+    <t>€2.75</t>
+  </si>
+  <si>
+    <t>€2.22</t>
+  </si>
+  <si>
+    <t>€2.0</t>
+  </si>
+  <si>
     <t>€1.9</t>
   </si>
   <si>
+    <t>€2.04</t>
+  </si>
+  <si>
+    <t>€1.05</t>
+  </si>
+  <si>
     <t>€1.8</t>
   </si>
   <si>
-    <t>€2.04</t>
-  </si>
-  <si>
-    <t>€1.05</t>
+    <t>€1.25</t>
   </si>
   <si>
     <t>€2.19</t>
   </si>
   <si>
-    <t>€1.25</t>
+    <t>€0.0</t>
+  </si>
+  <si>
+    <t>€1.7</t>
   </si>
   <si>
     <t>€1.58</t>
   </si>
   <si>
-    <t>€0.0</t>
-  </si>
-  <si>
-    <t>€1.7</t>
-  </si>
-  <si>
     <t>€1.5</t>
   </si>
   <si>
-    <t>€2.0</t>
+    <t>€0.8</t>
   </si>
   <si>
     <t>€1.32</t>
@@ -430,39 +475,51 @@
     <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662</t>
+  </si>
+  <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298</t>
+  </si>
+  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298</t>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366</t>
   </si>
   <si>
     <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359</t>
   </si>
   <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310836&amp;outcome=3862503623</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310842&amp;outcome=3862503635</t>
+  </si>
+  <si>
+    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625</t>
+  </si>
+  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621</t>
+    <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639905&amp;outcome=3856344588</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1024296378#event/1024296378</t>
   </si>
   <si>
-    <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625</t>
-  </si>
-  <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344568%7C2.25%7Creplace</t>
   </si>
   <si>
@@ -493,16 +550,22 @@
     <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865649377%7C2.75%7Creplace</t>
   </si>
   <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642398</t>
+  </si>
+  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642398</t>
+    <t>https://jacks.nl/sports/event/1023168666#event/1023168666</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224852#event/1023224852</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224902#event/1023224902</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224852?coupon=single%7C3865656372%7C1.58%7Creplace</t>
   </si>
   <si>
     <t>https://www.unibet.nl/betting/sports/event/1023168666?coupon=single%7C3862503622%7C2.02%7Creplace</t>
@@ -888,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -954,34 +1017,34 @@
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>2.2</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I3">
         <v>2.25</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L3">
         <v>10.1</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -998,34 +1061,34 @@
         <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>2.2</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I4">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="J4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="L4">
-        <v>9.09</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1042,34 +1105,34 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F5">
         <v>1.64</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I5">
         <v>3.3</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K5" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="L5">
         <v>8.720000000000001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1086,34 +1149,34 @@
         <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F6">
         <v>2.2</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I6">
         <v>2.1667</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L6">
         <v>8.390000000000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1130,34 +1193,34 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>2.48</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I7">
         <v>1.93</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="L7">
         <v>7.86</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1174,34 +1237,34 @@
         <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>1.64</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I8">
         <v>3.2</v>
       </c>
       <c r="J8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L8">
         <v>7.77</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1218,34 +1281,34 @@
         <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>1.81</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I9">
         <v>2.7</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L9">
         <v>7.71</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1262,34 +1325,34 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F10">
         <v>2.48</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I10">
         <v>1.9091</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L10">
         <v>7.3</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1306,34 +1369,34 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>2.48</v>
       </c>
       <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
         <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>52</v>
       </c>
       <c r="I11">
         <v>1.9</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="L11">
         <v>7.05</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1350,34 +1413,34 @@
         <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>1.81</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I12">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="L12">
-        <v>6.73</v>
+        <v>7.02</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1394,34 +1457,34 @@
         <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F13">
         <v>2.19</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I13">
         <v>2.06</v>
       </c>
       <c r="J13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="L13">
         <v>5.79</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1438,34 +1501,34 @@
         <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F14">
         <v>1.42</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I14">
         <v>4.1</v>
       </c>
       <c r="J14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="L14">
         <v>5.19</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1482,34 +1545,34 @@
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I15">
         <v>1.61</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L15">
         <v>4.55</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1526,34 +1589,34 @@
         <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F16">
         <v>1.42</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I16">
         <v>3.95</v>
       </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="L16">
         <v>4.26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1570,45 +1633,45 @@
         <v>39</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F17">
         <v>1.67</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I17">
         <v>2.75</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L17">
         <v>3.76</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
@@ -1617,207 +1680,207 @@
         <v>51</v>
       </c>
       <c r="F18">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I18">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="L18">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
         <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F19">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I19">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L19">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I20">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="J20" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L20">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F21">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I21">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="J21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="L21">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F22">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L22">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1825,43 +1888,43 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F23">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I23">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="L23">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1872,128 +1935,128 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F24">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I24">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="J24" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="L24">
-        <v>1.66</v>
+        <v>2.53</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F25">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I25">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="J25" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L25">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
         <v>36</v>
       </c>
       <c r="E26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F26">
         <v>2.85</v>
       </c>
       <c r="G26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I26">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K26" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L26">
-        <v>1.62</v>
+        <v>2.41</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2004,172 +2067,172 @@
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F27">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I27">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="J27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L27">
-        <v>1.52</v>
+        <v>2.38</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F28">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I28">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="L28">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
         <v>51</v>
       </c>
       <c r="F29">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I29">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K29" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="L29">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I30">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K30" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L30">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2180,260 +2243,656 @@
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F31">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="G31" t="s">
         <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I31">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="L31">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F32">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H32" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="I32">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="K32" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L32">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F33">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>1.58</v>
       </c>
       <c r="J33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K33" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L33">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F34">
-        <v>1.94</v>
+        <v>3.45</v>
       </c>
       <c r="G34" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I34">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="J34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K34" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L34">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
         <v>51</v>
       </c>
       <c r="F35">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H35" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I35">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="J35" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L35">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36">
+        <v>2.5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I36">
+        <v>1.71</v>
+      </c>
+      <c r="J36" t="s">
+        <v>91</v>
+      </c>
+      <c r="K36" t="s">
+        <v>137</v>
+      </c>
+      <c r="L36">
+        <v>1.52</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" t="s">
+        <v>55</v>
+      </c>
+      <c r="I37">
+        <v>1.13</v>
+      </c>
+      <c r="J37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" t="s">
+        <v>138</v>
+      </c>
+      <c r="L37">
+        <v>1.5</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38">
+        <v>1.85</v>
+      </c>
+      <c r="G38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I38">
+        <v>2.25</v>
+      </c>
+      <c r="J38" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" t="s">
+        <v>139</v>
+      </c>
+      <c r="L38">
+        <v>1.5</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39">
+        <v>3.5</v>
+      </c>
+      <c r="G39" t="s">
+        <v>65</v>
+      </c>
+      <c r="H39" t="s">
+        <v>55</v>
+      </c>
+      <c r="I39">
+        <v>1.43</v>
+      </c>
+      <c r="J39" t="s">
+        <v>101</v>
+      </c>
+      <c r="K39" t="s">
+        <v>140</v>
+      </c>
+      <c r="L39">
+        <v>1.5</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
         <v>20</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>21</v>
       </c>
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36">
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40">
+        <v>2.04</v>
+      </c>
+      <c r="G40" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40">
+        <v>2.02</v>
+      </c>
+      <c r="J40" t="s">
+        <v>95</v>
+      </c>
+      <c r="K40" t="s">
+        <v>141</v>
+      </c>
+      <c r="L40">
+        <v>1.48</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41">
+        <v>1.36</v>
+      </c>
+      <c r="G41" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" t="s">
+        <v>75</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41" t="s">
+        <v>105</v>
+      </c>
+      <c r="K41" t="s">
+        <v>131</v>
+      </c>
+      <c r="L41">
+        <v>1.47</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42">
+        <v>1.56</v>
+      </c>
+      <c r="G42" t="s">
+        <v>74</v>
+      </c>
+      <c r="H42" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42">
+        <v>2.9</v>
+      </c>
+      <c r="J42" t="s">
+        <v>106</v>
+      </c>
+      <c r="K42" t="s">
+        <v>142</v>
+      </c>
+      <c r="L42">
+        <v>1.41</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43">
+        <v>1.94</v>
+      </c>
+      <c r="G43" t="s">
+        <v>62</v>
+      </c>
+      <c r="H43" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43">
+        <v>2.12</v>
+      </c>
+      <c r="J43" t="s">
+        <v>107</v>
+      </c>
+      <c r="K43" t="s">
+        <v>143</v>
+      </c>
+      <c r="L43">
+        <v>1.28</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44">
+        <v>2.5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44">
+        <v>1.7</v>
+      </c>
+      <c r="J44" t="s">
+        <v>91</v>
+      </c>
+      <c r="K44" t="s">
+        <v>144</v>
+      </c>
+      <c r="L44">
+        <v>1.18</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s">
+        <v>49</v>
+      </c>
+      <c r="E45" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45">
         <v>2.8</v>
       </c>
-      <c r="G36" t="s">
-        <v>68</v>
-      </c>
-      <c r="H36" t="s">
-        <v>70</v>
-      </c>
-      <c r="I36">
+      <c r="G45" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" t="s">
+        <v>76</v>
+      </c>
+      <c r="I45">
         <v>1.5834</v>
       </c>
-      <c r="J36" t="s">
-        <v>98</v>
-      </c>
-      <c r="K36" t="s">
-        <v>130</v>
-      </c>
-      <c r="L36">
+      <c r="J45" t="s">
+        <v>96</v>
+      </c>
+      <c r="K45" t="s">
+        <v>145</v>
+      </c>
+      <c r="L45">
         <v>1.13</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>167</v>
+      <c r="M45" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2468,44 +2927,62 @@
     <hyperlink ref="N16" r:id="rId28" location="event/1023224918"/>
     <hyperlink ref="M17" r:id="rId29" location="/event/10035960"/>
     <hyperlink ref="N17" r:id="rId30"/>
-    <hyperlink ref="M18" r:id="rId31"/>
-    <hyperlink ref="N18" r:id="rId32"/>
-    <hyperlink ref="M19" r:id="rId33" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
-    <hyperlink ref="N19" r:id="rId34"/>
-    <hyperlink ref="M20" r:id="rId35"/>
-    <hyperlink ref="N20" r:id="rId36" location="event/1023224945"/>
+    <hyperlink ref="M18" r:id="rId31" location="event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662"/>
+    <hyperlink ref="N18" r:id="rId32" location="event/1023224918"/>
+    <hyperlink ref="M19" r:id="rId33"/>
+    <hyperlink ref="N19" r:id="rId34" location="event/1023224918"/>
+    <hyperlink ref="M20" r:id="rId35" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
+    <hyperlink ref="N20" r:id="rId36"/>
     <hyperlink ref="M21" r:id="rId37"/>
-    <hyperlink ref="N21" r:id="rId38" location="event/1023224945"/>
-    <hyperlink ref="M22" r:id="rId39" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
-    <hyperlink ref="N22" r:id="rId40" location="event/1023224852"/>
+    <hyperlink ref="N21" r:id="rId38"/>
+    <hyperlink ref="M22" r:id="rId39"/>
+    <hyperlink ref="N22" r:id="rId40" location="event/1023224945"/>
     <hyperlink ref="M23" r:id="rId41"/>
     <hyperlink ref="N23" r:id="rId42" location="event/1023224945"/>
-    <hyperlink ref="M24" r:id="rId43" location="event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662"/>
+    <hyperlink ref="M24" r:id="rId43"/>
     <hyperlink ref="N24" r:id="rId44" location="event/1023224918"/>
-    <hyperlink ref="M25" r:id="rId45" location="event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060"/>
-    <hyperlink ref="N25" r:id="rId46" location="event/1023224902"/>
+    <hyperlink ref="M25" r:id="rId45" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
+    <hyperlink ref="N25" r:id="rId46" location="event/1023168666"/>
     <hyperlink ref="M26" r:id="rId47" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
     <hyperlink ref="N26" r:id="rId48" location="event/1023224852"/>
-    <hyperlink ref="M27" r:id="rId49" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
-    <hyperlink ref="N27" r:id="rId50" location="event/1023224902"/>
-    <hyperlink ref="M28" r:id="rId51" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
-    <hyperlink ref="N28" r:id="rId52" location="event/1023224852"/>
-    <hyperlink ref="M29" r:id="rId53"/>
-    <hyperlink ref="N29" r:id="rId54" location="event/1023224945"/>
-    <hyperlink ref="M30" r:id="rId55"/>
-    <hyperlink ref="N30" r:id="rId56" location="event/1023224945"/>
+    <hyperlink ref="M27" r:id="rId49" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
+    <hyperlink ref="N27" r:id="rId50" location="event/1023224852"/>
+    <hyperlink ref="M28" r:id="rId51" location="event=1023168666&amp;betoffer=2551310836&amp;outcome=3862503623"/>
+    <hyperlink ref="N28" r:id="rId52" location="event/1023168666"/>
+    <hyperlink ref="M29" r:id="rId53" location="event=1023168666&amp;betoffer=2551310842&amp;outcome=3862503635"/>
+    <hyperlink ref="N29" r:id="rId54" location="event/1023168666"/>
+    <hyperlink ref="M30" r:id="rId55" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
+    <hyperlink ref="N30" r:id="rId56" location="event/1023168666"/>
     <hyperlink ref="M31" r:id="rId57"/>
     <hyperlink ref="N31" r:id="rId58" location="event/1023224945"/>
-    <hyperlink ref="M32" r:id="rId59" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
-    <hyperlink ref="N32" r:id="rId60"/>
-    <hyperlink ref="M33" r:id="rId61" location="/event/10035960"/>
+    <hyperlink ref="M32" r:id="rId59" location="event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060"/>
+    <hyperlink ref="N32" r:id="rId60" location="event/1023224902"/>
+    <hyperlink ref="M33" r:id="rId61" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
     <hyperlink ref="N33" r:id="rId62"/>
-    <hyperlink ref="M34" r:id="rId63" location="event/1024296378"/>
-    <hyperlink ref="N34" r:id="rId64" location="event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833"/>
-    <hyperlink ref="M35" r:id="rId65"/>
-    <hyperlink ref="N35" r:id="rId66" location="/event/10028349"/>
-    <hyperlink ref="M36" r:id="rId67" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
-    <hyperlink ref="N36" r:id="rId68"/>
+    <hyperlink ref="M34" r:id="rId63"/>
+    <hyperlink ref="N34" r:id="rId64" location="event/1023224918"/>
+    <hyperlink ref="M35" r:id="rId65" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
+    <hyperlink ref="N35" r:id="rId66" location="event/1023224852"/>
+    <hyperlink ref="M36" r:id="rId67" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
+    <hyperlink ref="N36" r:id="rId68" location="event/1023224902"/>
+    <hyperlink ref="M37" r:id="rId69"/>
+    <hyperlink ref="N37" r:id="rId70" location="event/1023224945"/>
+    <hyperlink ref="M38" r:id="rId71"/>
+    <hyperlink ref="N38" r:id="rId72" location="event/1023224945"/>
+    <hyperlink ref="M39" r:id="rId73"/>
+    <hyperlink ref="N39" r:id="rId74" location="event/1023224945"/>
+    <hyperlink ref="M40" r:id="rId75" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
+    <hyperlink ref="N40" r:id="rId76"/>
+    <hyperlink ref="M41" r:id="rId77" location="/event/10035960"/>
+    <hyperlink ref="N41" r:id="rId78"/>
+    <hyperlink ref="M42" r:id="rId79" location="event=1023224918&amp;betoffer=2549639905&amp;outcome=3856344588"/>
+    <hyperlink ref="N42" r:id="rId80" location="event/1023224918"/>
+    <hyperlink ref="M43" r:id="rId81" location="event/1024296378"/>
+    <hyperlink ref="N43" r:id="rId82" location="event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833"/>
+    <hyperlink ref="M44" r:id="rId83"/>
+    <hyperlink ref="N44" r:id="rId84" location="/event/10028349"/>
+    <hyperlink ref="M45" r:id="rId85" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
+    <hyperlink ref="N45" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="161">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,27 +58,27 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:03:24</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:08:08</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
   </si>
   <si>
+    <t>Litouwen vs Nederland</t>
+  </si>
+  <si>
+    <t>Duitsland vs Noord-Ierland</t>
+  </si>
+  <si>
+    <t>Turkije vs Spanje</t>
+  </si>
+  <si>
+    <t>Engeland vs Andorra</t>
+  </si>
+  <si>
     <t>Bolivia vs Brazilië</t>
   </si>
   <si>
-    <t>Litouwen vs Nederland</t>
-  </si>
-  <si>
-    <t>Turkije vs Spanje</t>
-  </si>
-  <si>
-    <t>Duitsland vs Noord-Ierland</t>
-  </si>
-  <si>
-    <t>Engeland vs Andorra</t>
-  </si>
-  <si>
     <t>totaal aantal schoten</t>
   </si>
   <si>
@@ -88,15 +88,15 @@
     <t>portugal</t>
   </si>
   <si>
+    <t>sem steijn</t>
+  </si>
+  <si>
+    <t>armenië</t>
+  </si>
+  <si>
     <t>wedstrijd</t>
   </si>
   <si>
-    <t>sem steijn</t>
-  </si>
-  <si>
-    <t>armenië</t>
-  </si>
-  <si>
     <t>spanje</t>
   </si>
   <si>
@@ -124,39 +124,39 @@
     <t>meer dan 18.5</t>
   </si>
   <si>
+    <t>meer dan 4.5</t>
+  </si>
+  <si>
+    <t>meer dan 16.5</t>
+  </si>
+  <si>
+    <t>meer dan 2.5</t>
+  </si>
+  <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
+    <t>meer dan 10.5</t>
+  </si>
+  <si>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
+    <t>meer dan 5.5</t>
+  </si>
+  <si>
+    <t>meer dan 3.5</t>
+  </si>
+  <si>
     <t>meer dan 8.5</t>
   </si>
   <si>
-    <t>meer dan 16.5</t>
-  </si>
-  <si>
-    <t>meer dan 4.5</t>
+    <t>meer dan 22.5</t>
   </si>
   <si>
     <t>meer dan 7.5</t>
   </si>
   <si>
-    <t>meer dan 2.5</t>
-  </si>
-  <si>
-    <t>meer dan 9.5</t>
-  </si>
-  <si>
-    <t>meer dan 6.5</t>
-  </si>
-  <si>
-    <t>meer dan 10.5</t>
-  </si>
-  <si>
-    <t>meer dan 5.5</t>
-  </si>
-  <si>
-    <t>meer dan 3.5</t>
-  </si>
-  <si>
-    <t>meer dan 22.5</t>
-  </si>
-  <si>
     <t>meer dan 23.5</t>
   </si>
   <si>
@@ -172,141 +172,123 @@
     <t>bingoal</t>
   </si>
   <si>
+    <t>vbet</t>
+  </si>
+  <si>
+    <t>toto</t>
+  </si>
+  <si>
+    <t>jacks</t>
+  </si>
+  <si>
+    <t>minder dan 19.5</t>
+  </si>
+  <si>
+    <t>minder dan 17.5</t>
+  </si>
+  <si>
+    <t>minder dan 20.5</t>
+  </si>
+  <si>
+    <t>minder dan 18.5</t>
+  </si>
+  <si>
+    <t>minder dan 4.5</t>
+  </si>
+  <si>
+    <t>minder dan 16.5</t>
+  </si>
+  <si>
+    <t>minder dan 2.5</t>
+  </si>
+  <si>
+    <t>minder dan 9.5</t>
+  </si>
+  <si>
+    <t>minder dan 10.5</t>
+  </si>
+  <si>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
+    <t>minder dan 5.5</t>
+  </si>
+  <si>
+    <t>minder dan 3.5</t>
+  </si>
+  <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
+    <t>minder dan 22.5</t>
+  </si>
+  <si>
+    <t>minder dan 7.5</t>
+  </si>
+  <si>
+    <t>minder dan 23.5</t>
+  </si>
+  <si>
+    <t>minder dan 21.5</t>
+  </si>
+  <si>
+    <t>minder dan 24.5</t>
+  </si>
+  <si>
+    <t>minder dan 1.5</t>
+  </si>
+  <si>
+    <t>starcasino</t>
+  </si>
+  <si>
     <t>onecasino</t>
   </si>
   <si>
-    <t>vbet</t>
-  </si>
-  <si>
-    <t>toto</t>
-  </si>
-  <si>
-    <t>jacks</t>
-  </si>
-  <si>
-    <t>minder dan 19.5</t>
-  </si>
-  <si>
-    <t>minder dan 17.5</t>
-  </si>
-  <si>
-    <t>minder dan 20.5</t>
-  </si>
-  <si>
-    <t>minder dan 18.5</t>
-  </si>
-  <si>
-    <t>minder dan 8.5</t>
-  </si>
-  <si>
-    <t>minder dan 16.5</t>
-  </si>
-  <si>
-    <t>minder dan 4.5</t>
-  </si>
-  <si>
-    <t>minder dan 7.5</t>
-  </si>
-  <si>
-    <t>minder dan 2.5</t>
-  </si>
-  <si>
-    <t>minder dan 9.5</t>
-  </si>
-  <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
-    <t>minder dan 10.5</t>
-  </si>
-  <si>
-    <t>minder dan 5.5</t>
-  </si>
-  <si>
-    <t>minder dan 3.5</t>
-  </si>
-  <si>
-    <t>minder dan 22.5</t>
-  </si>
-  <si>
-    <t>minder dan 23.5</t>
-  </si>
-  <si>
-    <t>minder dan 21.5</t>
-  </si>
-  <si>
-    <t>minder dan 24.5</t>
-  </si>
-  <si>
-    <t>minder dan 1.5</t>
-  </si>
-  <si>
-    <t>kambi</t>
-  </si>
-  <si>
-    <t>starcasino</t>
-  </si>
-  <si>
     <t>1=76, 2=74</t>
   </si>
   <si>
-    <t>1=100, 2=50</t>
-  </si>
-  <si>
     <t>1=74, 2=76</t>
   </si>
   <si>
-    <t>1=66, 2=84</t>
-  </si>
-  <si>
     <t>1=99, 2=51</t>
   </si>
   <si>
-    <t>1=90, 2=60</t>
-  </si>
-  <si>
     <t>1=65, 2=85</t>
   </si>
   <si>
     <t>1=89, 2=61</t>
   </si>
   <si>
+    <t>1=52, 2=98</t>
+  </si>
+  <si>
+    <t>1=110, 2=40</t>
+  </si>
+  <si>
+    <t>1=59, 2=91</t>
+  </si>
+  <si>
+    <t>1=61, 2=89</t>
+  </si>
+  <si>
+    <t>1=62, 2=88</t>
+  </si>
+  <si>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
+    <t>1=75, 2=75</t>
+  </si>
+  <si>
+    <t>1=54, 2=96</t>
+  </si>
+  <si>
     <t>1=73, 2=77</t>
   </si>
   <si>
-    <t>1=111, 2=39</t>
-  </si>
-  <si>
-    <t>1=52, 2=98</t>
-  </si>
-  <si>
-    <t>1=110, 2=40</t>
-  </si>
-  <si>
-    <t>1=93, 2=57</t>
-  </si>
-  <si>
-    <t>1=59, 2=91</t>
-  </si>
-  <si>
-    <t>1=61, 2=89</t>
-  </si>
-  <si>
-    <t>1=62, 2=88</t>
-  </si>
-  <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
-    <t>1=75, 2=75</t>
-  </si>
-  <si>
-    <t>1=54, 2=96</t>
-  </si>
-  <si>
     <t>1=86, 2=64</t>
   </si>
   <si>
@@ -316,72 +298,45 @@
     <t>1=84, 2=66</t>
   </si>
   <si>
-    <t>1=53, 2=97</t>
-  </si>
-  <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
     <t>1=95, 2=55</t>
   </si>
   <si>
+    <t>1=82, 2=68</t>
+  </si>
+  <si>
     <t>1=15, 2=135</t>
   </si>
   <si>
-    <t>1=82, 2=68</t>
-  </si>
-  <si>
-    <t>1=112, 2=38</t>
-  </si>
-  <si>
     <t>1=98, 2=52</t>
   </si>
   <si>
     <t>1=78, 2=72</t>
   </si>
   <si>
-    <t>€16.5</t>
-  </si>
-  <si>
     <t>€15.02</t>
   </si>
   <si>
-    <t>€14.0</t>
-  </si>
-  <si>
     <t>€12.8</t>
   </si>
   <si>
-    <t>€12.12</t>
-  </si>
-  <si>
     <t>€12.36</t>
   </si>
   <si>
-    <t>€12.0</t>
-  </si>
-  <si>
     <t>€11.2</t>
   </si>
   <si>
     <t>€11.09</t>
   </si>
   <si>
-    <t>€8.62</t>
-  </si>
-  <si>
-    <t>€7.62</t>
-  </si>
-  <si>
     <t>€6.0</t>
   </si>
   <si>
     <t>€6.2</t>
   </si>
   <si>
-    <t>€5.31</t>
-  </si>
-  <si>
     <t>€4.7</t>
   </si>
   <si>
@@ -418,9 +373,6 @@
     <t>€2.04</t>
   </si>
   <si>
-    <t>€1.05</t>
-  </si>
-  <si>
     <t>€1.8</t>
   </si>
   <si>
@@ -430,18 +382,15 @@
     <t>€2.19</t>
   </si>
   <si>
+    <t>€1.7</t>
+  </si>
+  <si>
+    <t>€1.58</t>
+  </si>
+  <si>
     <t>€0.0</t>
   </si>
   <si>
-    <t>€1.7</t>
-  </si>
-  <si>
-    <t>€1.58</t>
-  </si>
-  <si>
-    <t>€1.5</t>
-  </si>
-  <si>
     <t>€0.8</t>
   </si>
   <si>
@@ -466,27 +415,24 @@
     <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504</t>
   </si>
   <si>
-    <t>https://sports.onecasino.nl/#/event/10035960</t>
+    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
     <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487</t>
   </si>
   <si>
-    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
   </si>
   <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
+  </si>
+  <si>
     <t>https://www.bingoal.nl/sports/#event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
-  </si>
-  <si>
     <t>https://www.bingoal.nl/sports/#event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621</t>
   </si>
   <si>
@@ -520,42 +466,21 @@
     <t>https://jacks.nl/sports/event/1024296378#event/1024296378</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344568%7C2.25%7Creplace</t>
-  </si>
-  <si>
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344699%7C3.30%7Creplace</t>
-  </si>
-  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12631456</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3864494198%7C1.93%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344639%7C2.70%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865660847%7C2.06%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344605%7C4.10%7Creplace</t>
-  </si>
-  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865649377%7C2.75%7Creplace</t>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642398</t>
   </si>
   <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
-  </si>
-  <si>
     <t>https://jacks.nl/sports/event/1023168666#event/1023168666</t>
   </si>
   <si>
@@ -563,15 +488,6 @@
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224902#event/1023224902</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224852?coupon=single%7C3865656372%7C1.58%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023168666?coupon=single%7C3862503622%7C2.02%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1024296378?coupon=single%7C3865661081%7C4.00%7Creplace</t>
   </si>
   <si>
     <t>https://www.bingoal.nl/sports/#event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833</t>
@@ -951,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1023,28 +939,28 @@
         <v>2.2</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I3">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="J3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="L3">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1067,28 +983,28 @@
         <v>2.2</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="I4">
-        <v>2.23</v>
+        <v>2.1667</v>
       </c>
       <c r="J4" t="s">
         <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L4">
-        <v>9.699999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1111,28 +1027,28 @@
         <v>1.64</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="s">
         <v>78</v>
       </c>
       <c r="K5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L5">
-        <v>8.720000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1146,37 +1062,37 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>51</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I6">
-        <v>2.1667</v>
+        <v>1.9091</v>
       </c>
       <c r="J6" t="s">
         <v>79</v>
       </c>
       <c r="K6" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L6">
-        <v>8.390000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1199,28 +1115,28 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I7">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="L7">
-        <v>7.86</v>
+        <v>7.05</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1234,81 +1150,81 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>51</v>
       </c>
       <c r="F8">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K8" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L8">
-        <v>7.77</v>
+        <v>7.02</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="G9" t="s">
         <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I9">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="L9">
-        <v>7.71</v>
+        <v>4.55</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1322,37 +1238,37 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
         <v>51</v>
       </c>
       <c r="F10">
-        <v>2.48</v>
+        <v>1.42</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="I10">
-        <v>1.9091</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="L10">
-        <v>7.3</v>
+        <v>4.26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1360,43 +1276,43 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
         <v>51</v>
       </c>
       <c r="F11">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="s">
         <v>83</v>
       </c>
       <c r="K11" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L11">
-        <v>7.05</v>
+        <v>3.44</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1404,395 +1320,395 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I12">
-        <v>2.65</v>
+        <v>1.74</v>
       </c>
       <c r="J12" t="s">
         <v>84</v>
       </c>
       <c r="K12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="L12">
-        <v>7.02</v>
+        <v>3.31</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I13">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="J13" t="s">
         <v>85</v>
       </c>
       <c r="K13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L13">
-        <v>5.79</v>
+        <v>3.18</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
         <v>51</v>
       </c>
       <c r="F14">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I14">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="J14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="L14">
-        <v>5.19</v>
+        <v>3.18</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I15">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L15">
-        <v>4.55</v>
+        <v>3.08</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I16">
-        <v>3.95</v>
+        <v>2.23</v>
       </c>
       <c r="J16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L16">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I17">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L17">
-        <v>3.76</v>
+        <v>2.53</v>
       </c>
       <c r="M17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
         <v>51</v>
       </c>
       <c r="F18">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I18">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="L18">
-        <v>3.44</v>
+        <v>2.44</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F19">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="G19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I19">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L19">
-        <v>3.31</v>
+        <v>2.41</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E20" t="s">
         <v>51</v>
       </c>
       <c r="F20">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H20" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="I20">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="J20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L20">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1800,268 +1716,268 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F21">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="I21">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="L21">
-        <v>3.18</v>
+        <v>1.89</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>1.77</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I22">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="L22">
-        <v>3.08</v>
+        <v>1.84</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F23">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I23">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="L23">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="J24" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K24" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="L24">
-        <v>2.53</v>
+        <v>1.71</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>51</v>
       </c>
       <c r="F25">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I25">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L25">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="M25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N25" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F26">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I26">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="J26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L26">
-        <v>2.41</v>
+        <v>1.57</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
@@ -2070,345 +1986,345 @@
         <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
         <v>51</v>
       </c>
       <c r="F27">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L27">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
         <v>51</v>
       </c>
       <c r="F28">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I28">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="J28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L28">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F29">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I29">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="J29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K29" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L29">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F30">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I30">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="J30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="L30">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F31">
-        <v>2.45</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I31">
-        <v>1.74</v>
+        <v>1.13</v>
       </c>
       <c r="J31" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K31" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="L31">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
         <v>51</v>
       </c>
       <c r="F32">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I32">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K32" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="L32">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
       </c>
       <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33">
+        <v>1.94</v>
+      </c>
+      <c r="G33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" t="s">
         <v>51</v>
       </c>
-      <c r="F33">
-        <v>2.85</v>
-      </c>
-      <c r="G33" t="s">
-        <v>60</v>
-      </c>
-      <c r="H33" t="s">
-        <v>75</v>
-      </c>
       <c r="I33">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K33" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="L33">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="M33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="N33" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F34">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H34" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I34">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="L34">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2416,573 +2332,113 @@
         <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E35" t="s">
         <v>51</v>
       </c>
       <c r="F35">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H35" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="I35">
-        <v>2.75</v>
+        <v>1.5834</v>
       </c>
       <c r="J35" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="L35">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36">
-        <v>2.5</v>
-      </c>
-      <c r="G36" t="s">
-        <v>66</v>
-      </c>
-      <c r="H36" t="s">
-        <v>55</v>
-      </c>
-      <c r="I36">
-        <v>1.71</v>
-      </c>
-      <c r="J36" t="s">
-        <v>91</v>
-      </c>
-      <c r="K36" t="s">
-        <v>137</v>
-      </c>
-      <c r="L36">
-        <v>1.52</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
-      </c>
-      <c r="G37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" t="s">
-        <v>55</v>
-      </c>
-      <c r="I37">
-        <v>1.13</v>
-      </c>
-      <c r="J37" t="s">
-        <v>103</v>
-      </c>
-      <c r="K37" t="s">
-        <v>138</v>
-      </c>
-      <c r="L37">
-        <v>1.5</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38">
-        <v>1.85</v>
-      </c>
-      <c r="G38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" t="s">
-        <v>55</v>
-      </c>
-      <c r="I38">
-        <v>2.25</v>
-      </c>
-      <c r="J38" t="s">
-        <v>104</v>
-      </c>
-      <c r="K38" t="s">
-        <v>139</v>
-      </c>
-      <c r="L38">
-        <v>1.5</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39">
-        <v>3.5</v>
-      </c>
-      <c r="G39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H39" t="s">
-        <v>55</v>
-      </c>
-      <c r="I39">
-        <v>1.43</v>
-      </c>
-      <c r="J39" t="s">
-        <v>101</v>
-      </c>
-      <c r="K39" t="s">
-        <v>140</v>
-      </c>
-      <c r="L39">
-        <v>1.5</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40">
-        <v>2.04</v>
-      </c>
-      <c r="G40" t="s">
-        <v>70</v>
-      </c>
-      <c r="H40" t="s">
-        <v>75</v>
-      </c>
-      <c r="I40">
-        <v>2.02</v>
-      </c>
-      <c r="J40" t="s">
-        <v>95</v>
-      </c>
-      <c r="K40" t="s">
-        <v>141</v>
-      </c>
-      <c r="L40">
-        <v>1.48</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41">
-        <v>1.36</v>
-      </c>
-      <c r="G41" t="s">
-        <v>66</v>
-      </c>
-      <c r="H41" t="s">
-        <v>75</v>
-      </c>
-      <c r="I41">
-        <v>4</v>
-      </c>
-      <c r="J41" t="s">
-        <v>105</v>
-      </c>
-      <c r="K41" t="s">
-        <v>131</v>
-      </c>
-      <c r="L41">
-        <v>1.47</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42">
-        <v>1.56</v>
-      </c>
-      <c r="G42" t="s">
-        <v>74</v>
-      </c>
-      <c r="H42" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42">
-        <v>2.9</v>
-      </c>
-      <c r="J42" t="s">
-        <v>106</v>
-      </c>
-      <c r="K42" t="s">
-        <v>142</v>
-      </c>
-      <c r="L42">
-        <v>1.41</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" t="s">
-        <v>55</v>
-      </c>
-      <c r="F43">
-        <v>1.94</v>
-      </c>
-      <c r="G43" t="s">
-        <v>62</v>
-      </c>
-      <c r="H43" t="s">
-        <v>51</v>
-      </c>
-      <c r="I43">
-        <v>2.12</v>
-      </c>
-      <c r="J43" t="s">
-        <v>107</v>
-      </c>
-      <c r="K43" t="s">
-        <v>143</v>
-      </c>
-      <c r="L43">
-        <v>1.28</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44">
-        <v>2.5</v>
-      </c>
-      <c r="G44" t="s">
-        <v>67</v>
-      </c>
-      <c r="H44" t="s">
-        <v>52</v>
-      </c>
-      <c r="I44">
-        <v>1.7</v>
-      </c>
-      <c r="J44" t="s">
-        <v>91</v>
-      </c>
-      <c r="K44" t="s">
-        <v>144</v>
-      </c>
-      <c r="L44">
-        <v>1.18</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45">
-        <v>2.8</v>
-      </c>
-      <c r="G45" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" t="s">
-        <v>76</v>
-      </c>
-      <c r="I45">
-        <v>1.5834</v>
-      </c>
-      <c r="J45" t="s">
-        <v>96</v>
-      </c>
-      <c r="K45" t="s">
-        <v>145</v>
-      </c>
-      <c r="L45">
-        <v>1.13</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
-    <hyperlink ref="N3" r:id="rId2"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
     <hyperlink ref="M4" r:id="rId3" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
-    <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
+    <hyperlink ref="N4" r:id="rId4"/>
     <hyperlink ref="M5" r:id="rId5" location="event=1023224918&amp;betoffer=2549639875&amp;outcome=3856344538"/>
-    <hyperlink ref="N5" r:id="rId6"/>
-    <hyperlink ref="M6" r:id="rId7" location="event=1023224918&amp;betoffer=2549639833&amp;outcome=3856344463"/>
+    <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
+    <hyperlink ref="M6" r:id="rId7" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
     <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
-    <hyperlink ref="N7" r:id="rId10"/>
-    <hyperlink ref="M8" r:id="rId11" location="event=1023224918&amp;betoffer=2549639875&amp;outcome=3856344538"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224918"/>
+    <hyperlink ref="M8" r:id="rId11" location="event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504"/>
     <hyperlink ref="N8" r:id="rId12" location="event/1023224918"/>
-    <hyperlink ref="M9" r:id="rId13" location="event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504"/>
-    <hyperlink ref="N9" r:id="rId14"/>
-    <hyperlink ref="M10" r:id="rId15" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
-    <hyperlink ref="N10" r:id="rId16"/>
-    <hyperlink ref="M11" r:id="rId17" location="event=1023224918&amp;betoffer=2551851711&amp;outcome=3864494197"/>
+    <hyperlink ref="M9" r:id="rId13"/>
+    <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
+    <hyperlink ref="M10" r:id="rId15" location="event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487"/>
+    <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
+    <hyperlink ref="M11" r:id="rId17" location="event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662"/>
     <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
-    <hyperlink ref="M12" r:id="rId19" location="event=1023224918&amp;betoffer=2549639857&amp;outcome=3856344504"/>
+    <hyperlink ref="M12" r:id="rId19"/>
     <hyperlink ref="N12" r:id="rId20" location="event/1023224918"/>
-    <hyperlink ref="M13" r:id="rId21" location="/event/10035960"/>
+    <hyperlink ref="M13" r:id="rId21"/>
     <hyperlink ref="N13" r:id="rId22"/>
-    <hyperlink ref="M14" r:id="rId23" location="event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487"/>
+    <hyperlink ref="M14" r:id="rId23" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
     <hyperlink ref="N14" r:id="rId24"/>
     <hyperlink ref="M15" r:id="rId25"/>
     <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
-    <hyperlink ref="M16" r:id="rId27" location="event=1023224918&amp;betoffer=2549639847&amp;outcome=3856344487"/>
-    <hyperlink ref="N16" r:id="rId28" location="event/1023224918"/>
-    <hyperlink ref="M17" r:id="rId29" location="/event/10035960"/>
-    <hyperlink ref="N17" r:id="rId30"/>
-    <hyperlink ref="M18" r:id="rId31" location="event=1023224918&amp;betoffer=2549639949&amp;outcome=3856344662"/>
-    <hyperlink ref="N18" r:id="rId32" location="event/1023224918"/>
-    <hyperlink ref="M19" r:id="rId33"/>
-    <hyperlink ref="N19" r:id="rId34" location="event/1023224918"/>
-    <hyperlink ref="M20" r:id="rId35" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
-    <hyperlink ref="N20" r:id="rId36"/>
-    <hyperlink ref="M21" r:id="rId37"/>
-    <hyperlink ref="N21" r:id="rId38"/>
-    <hyperlink ref="M22" r:id="rId39"/>
-    <hyperlink ref="N22" r:id="rId40" location="event/1023224945"/>
-    <hyperlink ref="M23" r:id="rId41"/>
-    <hyperlink ref="N23" r:id="rId42" location="event/1023224945"/>
+    <hyperlink ref="M16" r:id="rId27"/>
+    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
+    <hyperlink ref="M17" r:id="rId29"/>
+    <hyperlink ref="N17" r:id="rId30" location="event/1023224918"/>
+    <hyperlink ref="M18" r:id="rId31" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
+    <hyperlink ref="N18" r:id="rId32" location="event/1023168666"/>
+    <hyperlink ref="M19" r:id="rId33" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
+    <hyperlink ref="N19" r:id="rId34" location="event/1023224852"/>
+    <hyperlink ref="M20" r:id="rId35" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
+    <hyperlink ref="N20" r:id="rId36" location="event/1023224852"/>
+    <hyperlink ref="M21" r:id="rId37" location="event=1023168666&amp;betoffer=2551310836&amp;outcome=3862503623"/>
+    <hyperlink ref="N21" r:id="rId38" location="event/1023168666"/>
+    <hyperlink ref="M22" r:id="rId39" location="event=1023168666&amp;betoffer=2551310842&amp;outcome=3862503635"/>
+    <hyperlink ref="N22" r:id="rId40" location="event/1023168666"/>
+    <hyperlink ref="M23" r:id="rId41" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
+    <hyperlink ref="N23" r:id="rId42" location="event/1023168666"/>
     <hyperlink ref="M24" r:id="rId43"/>
-    <hyperlink ref="N24" r:id="rId44" location="event/1023224918"/>
-    <hyperlink ref="M25" r:id="rId45" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
-    <hyperlink ref="N25" r:id="rId46" location="event/1023168666"/>
-    <hyperlink ref="M26" r:id="rId47" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
-    <hyperlink ref="N26" r:id="rId48" location="event/1023224852"/>
-    <hyperlink ref="M27" r:id="rId49" location="event=1023224852&amp;betoffer=2552162167&amp;outcome=3865656359"/>
+    <hyperlink ref="N24" r:id="rId44" location="event/1023224945"/>
+    <hyperlink ref="M25" r:id="rId45" location="event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060"/>
+    <hyperlink ref="N25" r:id="rId46" location="event/1023224902"/>
+    <hyperlink ref="M26" r:id="rId47"/>
+    <hyperlink ref="N26" r:id="rId48" location="event/1023224918"/>
+    <hyperlink ref="M27" r:id="rId49" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
     <hyperlink ref="N27" r:id="rId50" location="event/1023224852"/>
-    <hyperlink ref="M28" r:id="rId51" location="event=1023168666&amp;betoffer=2551310836&amp;outcome=3862503623"/>
-    <hyperlink ref="N28" r:id="rId52" location="event/1023168666"/>
-    <hyperlink ref="M29" r:id="rId53" location="event=1023168666&amp;betoffer=2551310842&amp;outcome=3862503635"/>
-    <hyperlink ref="N29" r:id="rId54" location="event/1023168666"/>
-    <hyperlink ref="M30" r:id="rId55" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
-    <hyperlink ref="N30" r:id="rId56" location="event/1023168666"/>
+    <hyperlink ref="M28" r:id="rId51" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
+    <hyperlink ref="N28" r:id="rId52" location="event/1023224902"/>
+    <hyperlink ref="M29" r:id="rId53"/>
+    <hyperlink ref="N29" r:id="rId54" location="event/1023224945"/>
+    <hyperlink ref="M30" r:id="rId55"/>
+    <hyperlink ref="N30" r:id="rId56" location="event/1023224945"/>
     <hyperlink ref="M31" r:id="rId57"/>
     <hyperlink ref="N31" r:id="rId58" location="event/1023224945"/>
-    <hyperlink ref="M32" r:id="rId59" location="event=1023224902&amp;betoffer=2552148385&amp;outcome=3865627060"/>
-    <hyperlink ref="N32" r:id="rId60" location="event/1023224902"/>
-    <hyperlink ref="M33" r:id="rId61" location="event=1023224852&amp;betoffer=2552162170&amp;outcome=3865656366"/>
-    <hyperlink ref="N33" r:id="rId62"/>
+    <hyperlink ref="M32" r:id="rId59" location="event=1023224918&amp;betoffer=2549639905&amp;outcome=3856344588"/>
+    <hyperlink ref="N32" r:id="rId60" location="event/1023224918"/>
+    <hyperlink ref="M33" r:id="rId61" location="event/1024296378"/>
+    <hyperlink ref="N33" r:id="rId62" location="event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833"/>
     <hyperlink ref="M34" r:id="rId63"/>
-    <hyperlink ref="N34" r:id="rId64" location="event/1023224918"/>
-    <hyperlink ref="M35" r:id="rId65" location="event=1023224852&amp;betoffer=2552162169&amp;outcome=3865656364"/>
-    <hyperlink ref="N35" r:id="rId66" location="event/1023224852"/>
-    <hyperlink ref="M36" r:id="rId67" location="event=1023224902&amp;betoffer=2552148742&amp;outcome=3865645298"/>
-    <hyperlink ref="N36" r:id="rId68" location="event/1023224902"/>
-    <hyperlink ref="M37" r:id="rId69"/>
-    <hyperlink ref="N37" r:id="rId70" location="event/1023224945"/>
-    <hyperlink ref="M38" r:id="rId71"/>
-    <hyperlink ref="N38" r:id="rId72" location="event/1023224945"/>
-    <hyperlink ref="M39" r:id="rId73"/>
-    <hyperlink ref="N39" r:id="rId74" location="event/1023224945"/>
-    <hyperlink ref="M40" r:id="rId75" location="event=1023168666&amp;betoffer=2551310835&amp;outcome=3862503621"/>
-    <hyperlink ref="N40" r:id="rId76"/>
-    <hyperlink ref="M41" r:id="rId77" location="/event/10035960"/>
-    <hyperlink ref="N41" r:id="rId78"/>
-    <hyperlink ref="M42" r:id="rId79" location="event=1023224918&amp;betoffer=2549639905&amp;outcome=3856344588"/>
-    <hyperlink ref="N42" r:id="rId80" location="event/1023224918"/>
-    <hyperlink ref="M43" r:id="rId81" location="event/1024296378"/>
-    <hyperlink ref="N43" r:id="rId82" location="event=1024296378&amp;betoffer=2552168102&amp;outcome=3865660833"/>
-    <hyperlink ref="M44" r:id="rId83"/>
-    <hyperlink ref="N44" r:id="rId84" location="/event/10028349"/>
-    <hyperlink ref="M45" r:id="rId85" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
-    <hyperlink ref="N45" r:id="rId86"/>
+    <hyperlink ref="N34" r:id="rId64" location="/event/10028349"/>
+    <hyperlink ref="M35" r:id="rId65" location="event=1023168666&amp;betoffer=2551310837&amp;outcome=3862503625"/>
+    <hyperlink ref="N35" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,27 +58,21 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:17:16</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:21:30</t>
+  </si>
+  <si>
+    <t>Armenië vs Portugal</t>
+  </si>
+  <si>
+    <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
-    <t>Armenië vs Portugal</t>
-  </si>
-  <si>
-    <t>Duitsland vs Noord-Ierland</t>
-  </si>
-  <si>
-    <t>totaal aantal schoten</t>
-  </si>
-  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
-    <t>sem steijn</t>
-  </si>
-  <si>
     <t>armenië</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>nederland</t>
   </si>
   <si>
-    <t>meer dan 4.5</t>
-  </si>
-  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
@@ -100,30 +91,18 @@
     <t>meer dan 10.5</t>
   </si>
   <si>
-    <t>meer dan 5.5</t>
-  </si>
-  <si>
-    <t>meer dan 3.5</t>
-  </si>
-  <si>
     <t>meer dan 8.5</t>
   </si>
   <si>
+    <t>meer dan 1.5</t>
+  </si>
+  <si>
     <t>meer dan 7.5</t>
   </si>
   <si>
-    <t>meer dan 6.5</t>
-  </si>
-  <si>
-    <t>vbet</t>
-  </si>
-  <si>
     <t>toto</t>
   </si>
   <si>
-    <t>minder dan 4.5</t>
-  </si>
-  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
@@ -133,33 +112,27 @@
     <t>minder dan 10.5</t>
   </si>
   <si>
-    <t>minder dan 5.5</t>
-  </si>
-  <si>
-    <t>minder dan 3.5</t>
-  </si>
-  <si>
     <t>minder dan 8.5</t>
   </si>
   <si>
+    <t>minder dan 1.5</t>
+  </si>
+  <si>
     <t>minder dan 7.5</t>
   </si>
   <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
     <t>jacks</t>
   </si>
   <si>
+    <t>kambi</t>
+  </si>
+  <si>
     <t>starcasino</t>
   </si>
   <si>
     <t>onecasino</t>
   </si>
   <si>
-    <t>1=52, 2=98</t>
-  </si>
-  <si>
     <t>1=59, 2=91</t>
   </si>
   <si>
@@ -169,24 +142,24 @@
     <t>1=62, 2=88</t>
   </si>
   <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
     <t>1=81, 2=69</t>
   </si>
   <si>
+    <t>1=60, 2=90</t>
+  </si>
+  <si>
+    <t>1=98, 2=52</t>
+  </si>
+  <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
+    <t>1=80, 2=70</t>
+  </si>
+  <si>
     <t>1=82, 2=68</t>
   </si>
   <si>
-    <t>1=15, 2=135</t>
-  </si>
-  <si>
-    <t>€6.0</t>
-  </si>
-  <si>
     <t>€4.7</t>
   </si>
   <si>
@@ -199,27 +172,27 @@
     <t>€3.87</t>
   </si>
   <si>
+    <t>€3.0</t>
+  </si>
+  <si>
     <t>€1.9</t>
   </si>
   <si>
     <t>€1.8</t>
   </si>
   <si>
+    <t>€2.0</t>
+  </si>
+  <si>
+    <t>€1.58</t>
+  </si>
+  <si>
     <t>€1.7</t>
   </si>
   <si>
-    <t>€0.0</t>
-  </si>
-  <si>
-    <t>€1.58</t>
-  </si>
-  <si>
     <t>€1.3</t>
   </si>
   <si>
-    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
-  </si>
-  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
   </si>
   <si>
@@ -229,13 +202,22 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
+    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.74%7Creplace</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.23%7Creplace</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.44%7Creplace</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -669,84 +651,84 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
-        <v>44</v>
-      </c>
       <c r="I3">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="L3">
-        <v>4.55</v>
+        <v>3.44</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
         <v>36</v>
       </c>
-      <c r="H4" t="s">
-        <v>44</v>
-      </c>
       <c r="I4">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L4">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -754,87 +736,87 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
-        <v>44</v>
-      </c>
       <c r="I5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L5">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I6">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6">
+        <v>2.53</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L6">
-        <v>3.18</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -848,125 +830,125 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
       <c r="F7">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L7">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L8">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9">
+        <v>2.95</v>
+      </c>
+      <c r="J9" t="s">
         <v>44</v>
       </c>
-      <c r="I9">
-        <v>2.23</v>
-      </c>
-      <c r="J9" t="s">
-        <v>52</v>
-      </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L9">
-        <v>2.53</v>
+        <v>1.59</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -974,283 +956,283 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L10">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I11">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11">
+        <v>1.5</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="L11">
-        <v>1.57</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I12">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="L12">
         <v>1.5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I13">
-        <v>1.13</v>
+        <v>2.25</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L13">
         <v>1.5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I14">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L14">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="G15" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I15">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L15">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
     <hyperlink ref="M4" r:id="rId3"/>
-    <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
+    <hyperlink ref="N4" r:id="rId4"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
+    <hyperlink ref="N5" r:id="rId6"/>
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10" location="event/1023224945"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224918"/>
     <hyperlink ref="M8" r:id="rId11"/>
     <hyperlink ref="N8" r:id="rId12" location="event/1023224945"/>
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14" location="event/1023224918"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16" location="event/1023224945"/>
+    <hyperlink ref="N10" r:id="rId16"/>
     <hyperlink ref="M11" r:id="rId17"/>
     <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
     <hyperlink ref="M12" r:id="rId19"/>
@@ -1258,9 +1240,9 @@
     <hyperlink ref="M13" r:id="rId21"/>
     <hyperlink ref="N13" r:id="rId22" location="event/1023224945"/>
     <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24" location="event/1023224945"/>
+    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="/event/10028349"/>
+    <hyperlink ref="N15" r:id="rId26" location="event/1023224918"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:21:30</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:27:43</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -73,27 +73,27 @@
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
+    <t>wedstrijd</t>
+  </si>
+  <si>
     <t>armenië</t>
   </si>
   <si>
-    <t>wedstrijd</t>
-  </si>
-  <si>
     <t>nederland</t>
   </si>
   <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
-    <t>meer dan 9.5</t>
+    <t>meer dan 8.5</t>
   </si>
   <si>
     <t>meer dan 10.5</t>
   </si>
   <si>
-    <t>meer dan 8.5</t>
-  </si>
-  <si>
     <t>meer dan 1.5</t>
   </si>
   <si>
@@ -103,18 +103,18 @@
     <t>toto</t>
   </si>
   <si>
+    <t>minder dan 9.5</t>
+  </si>
+  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
-    <t>minder dan 9.5</t>
+    <t>minder dan 8.5</t>
   </si>
   <si>
     <t>minder dan 10.5</t>
   </si>
   <si>
-    <t>minder dan 8.5</t>
-  </si>
-  <si>
     <t>minder dan 1.5</t>
   </si>
   <si>
@@ -130,13 +130,13 @@
     <t>starcasino</t>
   </si>
   <si>
-    <t>onecasino</t>
+    <t>1=61, 2=89</t>
   </si>
   <si>
     <t>1=59, 2=91</t>
   </si>
   <si>
-    <t>1=61, 2=89</t>
+    <t>1=82, 2=68</t>
   </si>
   <si>
     <t>1=62, 2=88</t>
@@ -145,19 +145,25 @@
     <t>1=81, 2=69</t>
   </si>
   <si>
-    <t>1=60, 2=90</t>
-  </si>
-  <si>
-    <t>1=98, 2=52</t>
+    <t>1=45, 2=105</t>
+  </si>
+  <si>
+    <t>1=99, 2=51</t>
+  </si>
+  <si>
+    <t>1=102, 2=48</t>
   </si>
   <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
-    <t>1=80, 2=70</t>
-  </si>
-  <si>
-    <t>1=82, 2=68</t>
+    <t>€5.55</t>
+  </si>
+  <si>
+    <t>€5.61</t>
+  </si>
+  <si>
+    <t>€5.04</t>
   </si>
   <si>
     <t>€4.7</t>
@@ -172,27 +178,27 @@
     <t>€3.87</t>
   </si>
   <si>
+    <t>€3.3</t>
+  </si>
+  <si>
     <t>€3.0</t>
   </si>
   <si>
     <t>€1.9</t>
   </si>
   <si>
+    <t>€1.2</t>
+  </si>
+  <si>
     <t>€1.8</t>
   </si>
   <si>
-    <t>€2.0</t>
+    <t>€1.7</t>
   </si>
   <si>
     <t>€1.58</t>
   </si>
   <si>
-    <t>€1.7</t>
-  </si>
-  <si>
-    <t>€1.3</t>
-  </si>
-  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
   </si>
   <si>
@@ -205,6 +211,9 @@
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.70%7Creplace</t>
+  </si>
+  <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.74%7Creplace</t>
   </si>
   <si>
@@ -218,9 +227,6 @@
   </si>
   <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.44%7Creplace</t>
-  </si>
-  <si>
-    <t>https://sports.onecasino.nl/#/event/10028349</t>
   </si>
 </sst>
 </file>
@@ -591,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -660,7 +666,7 @@
         <v>28</v>
       </c>
       <c r="F3">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="G3" t="s">
         <v>29</v>
@@ -669,22 +675,22 @@
         <v>35</v>
       </c>
       <c r="I3">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L3">
-        <v>3.44</v>
+        <v>4.29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -704,42 +710,42 @@
         <v>28</v>
       </c>
       <c r="F4">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L4">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -748,28 +754,28 @@
         <v>28</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L5">
-        <v>3.18</v>
+        <v>3.51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>64</v>
@@ -786,34 +792,34 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L6">
-        <v>2.53</v>
+        <v>3.44</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>65</v>
@@ -827,10 +833,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -839,39 +845,39 @@
         <v>2.55</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I7">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L7">
-        <v>2.3</v>
+        <v>3.31</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -880,31 +886,31 @@
         <v>28</v>
       </c>
       <c r="F8">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="J8" t="s">
         <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8">
-        <v>1.71</v>
+        <v>3.18</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -918,37 +924,37 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K9" t="s">
         <v>53</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>2.53</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -959,10 +965,10 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -971,28 +977,28 @@
         <v>3.45</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
         <v>54</v>
       </c>
       <c r="L10">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1006,37 +1012,37 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="F11">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" t="s">
         <v>35</v>
       </c>
       <c r="I11">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1050,48 +1056,48 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="F12">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
         <v>35</v>
       </c>
       <c r="I12">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
       </c>
       <c r="L12">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -1100,7 +1106,7 @@
         <v>28</v>
       </c>
       <c r="F13">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="s">
         <v>34</v>
@@ -1109,110 +1115,154 @@
         <v>35</v>
       </c>
       <c r="I13">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
         <v>57</v>
       </c>
       <c r="L13">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
       </c>
       <c r="F14">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I14">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
         <v>58</v>
       </c>
       <c r="L14">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
       </c>
       <c r="F15">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
         <v>35</v>
       </c>
       <c r="I15">
+        <v>2.25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>3.5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
         <v>1.43</v>
       </c>
-      <c r="J15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15">
-        <v>1.08</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>62</v>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1220,29 +1270,31 @@
     <hyperlink ref="M3" r:id="rId1"/>
     <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
     <hyperlink ref="M4" r:id="rId3"/>
-    <hyperlink ref="N4" r:id="rId4"/>
+    <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6"/>
+    <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10" location="event/1023224918"/>
+    <hyperlink ref="N7" r:id="rId10"/>
     <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12" location="event/1023224945"/>
+    <hyperlink ref="N8" r:id="rId12"/>
     <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14" location="event/1023224918"/>
+    <hyperlink ref="N9" r:id="rId14"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16"/>
+    <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
     <hyperlink ref="M11" r:id="rId17"/>
     <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
     <hyperlink ref="M12" r:id="rId19"/>
     <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
     <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22" location="event/1023224945"/>
+    <hyperlink ref="N13" r:id="rId22" location="event/1023224918"/>
     <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
+    <hyperlink ref="N14" r:id="rId24"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="event/1023224918"/>
+    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
+    <hyperlink ref="M16" r:id="rId27"/>
+    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:27:43</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:31:10</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -124,12 +124,15 @@
     <t>jacks</t>
   </si>
   <si>
-    <t>kambi</t>
+    <t>betmgm</t>
   </si>
   <si>
     <t>starcasino</t>
   </si>
   <si>
+    <t>onecasino</t>
+  </si>
+  <si>
     <t>1=61, 2=89</t>
   </si>
   <si>
@@ -193,6 +196,9 @@
     <t>€1.8</t>
   </si>
   <si>
+    <t>€2.19</t>
+  </si>
+  <si>
     <t>€1.7</t>
   </si>
   <si>
@@ -211,22 +217,25 @@
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.70%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.74%7Creplace</t>
+    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.70%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.74%7Creplace</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.23%7Creplace</t>
+    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.23%7Creplace</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.44%7Creplace</t>
+    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.44%7Creplace</t>
+  </si>
+  <si>
+    <t>https://sports.onecasino.nl/#/event/10028349</t>
   </si>
 </sst>
 </file>
@@ -597,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -678,19 +687,19 @@
         <v>1.77</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3">
         <v>4.29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -722,19 +731,19 @@
         <v>1.71</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4">
         <v>3.78</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -766,19 +775,19 @@
         <v>2.28</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5">
         <v>3.51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -810,19 +819,19 @@
         <v>1.7</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L6">
         <v>3.44</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -854,19 +863,19 @@
         <v>1.74</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L7">
         <v>3.31</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -898,19 +907,19 @@
         <v>1.76</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L8">
         <v>3.18</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -942,19 +951,19 @@
         <v>2.23</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L9">
         <v>2.53</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -986,19 +995,19 @@
         <v>1.46</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L10">
         <v>2.52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1030,19 +1039,19 @@
         <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L11">
         <v>2.15</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1074,19 +1083,19 @@
         <v>1.74</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12">
         <v>1.71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1118,19 +1127,19 @@
         <v>3.15</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L13">
         <v>1.59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1162,63 +1171,63 @@
         <v>1.44</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14">
         <v>1.57</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I15">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1232,37 +1241,81 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
       </c>
       <c r="F16">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
       </c>
       <c r="I16">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L16">
         <v>1.5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17">
+        <v>3.5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17">
+        <v>1.43</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17">
+        <v>1.5</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1292,9 +1345,11 @@
     <hyperlink ref="M14" r:id="rId23"/>
     <hyperlink ref="N14" r:id="rId24"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
+    <hyperlink ref="N15" r:id="rId26" location="/event/10028349"/>
     <hyperlink ref="M16" r:id="rId27"/>
     <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
+    <hyperlink ref="M17" r:id="rId29"/>
+    <hyperlink ref="N17" r:id="rId30" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:31:10</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:33:06</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="64">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:33:06</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:35:54</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -124,9 +124,6 @@
     <t>jacks</t>
   </si>
   <si>
-    <t>betmgm</t>
-  </si>
-  <si>
     <t>starcasino</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>1=62, 2=88</t>
   </si>
   <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
     <t>1=45, 2=105</t>
   </si>
   <si>
@@ -169,18 +163,9 @@
     <t>€5.04</t>
   </si>
   <si>
-    <t>€4.7</t>
-  </si>
-  <si>
-    <t>€4.86</t>
-  </si>
-  <si>
     <t>€4.88</t>
   </si>
   <si>
-    <t>€3.87</t>
-  </si>
-  <si>
     <t>€3.3</t>
   </si>
   <si>
@@ -193,9 +178,6 @@
     <t>€1.2</t>
   </si>
   <si>
-    <t>€1.8</t>
-  </si>
-  <si>
     <t>€2.19</t>
   </si>
   <si>
@@ -217,22 +199,10 @@
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
-    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.70%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.74%7Creplace</t>
-  </si>
-  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
-    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.23%7Creplace</t>
-  </si>
-  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
-  </si>
-  <si>
-    <t>https://www.betmgm.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.44%7Creplace</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -606,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -687,19 +657,19 @@
         <v>1.77</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L3">
         <v>4.29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -731,19 +701,19 @@
         <v>1.71</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L4">
         <v>3.78</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -775,63 +745,63 @@
         <v>2.28</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L5">
         <v>3.51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -845,92 +815,92 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
       </c>
       <c r="F7">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L7">
-        <v>3.31</v>
+        <v>2.52</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L8">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -939,31 +909,31 @@
         <v>28</v>
       </c>
       <c r="F9">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L9">
-        <v>2.53</v>
+        <v>1.71</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -977,81 +947,81 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10">
-        <v>3.45</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
       <c r="I10">
-        <v>1.46</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="s">
         <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L10">
-        <v>2.52</v>
+        <v>1.59</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="F11">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L11">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="M11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1065,257 +1035,81 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="F12">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
         <v>35</v>
       </c>
       <c r="I12">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L12">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L13">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14">
-        <v>3.45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14">
-        <v>1.44</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14">
-        <v>1.57</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15">
-        <v>2.5</v>
-      </c>
-      <c r="G15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15">
-        <v>1.71</v>
-      </c>
-      <c r="J15" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15">
-        <v>1.52</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <v>1.85</v>
-      </c>
-      <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16">
-        <v>2.25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L16">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>3.5</v>
-      </c>
-      <c r="G17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17">
-        <v>1.43</v>
-      </c>
-      <c r="J17" t="s">
-        <v>47</v>
-      </c>
-      <c r="K17" t="s">
         <v>62</v>
-      </c>
-      <c r="L17">
-        <v>1.5</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1329,27 +1123,19 @@
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224918"/>
     <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12"/>
+    <hyperlink ref="N8" r:id="rId12" location="event/1023224918"/>
     <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14"/>
+    <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
     <hyperlink ref="M10" r:id="rId15"/>
     <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
     <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
+    <hyperlink ref="N11" r:id="rId18" location="/event/10028349"/>
     <hyperlink ref="M12" r:id="rId19"/>
     <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
     <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22" location="event/1023224918"/>
-    <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24"/>
-    <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="/event/10028349"/>
-    <hyperlink ref="M16" r:id="rId27"/>
-    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
-    <hyperlink ref="M17" r:id="rId29"/>
-    <hyperlink ref="N17" r:id="rId30" location="event/1023224945"/>
+    <hyperlink ref="N13" r:id="rId22" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:35:54</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:42:00</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="74">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:42:00</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:48:36</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -70,6 +70,9 @@
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
+    <t>Engeland vs Andorra</t>
+  </si>
+  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
@@ -85,12 +88,12 @@
     <t>meer dan 9.5</t>
   </si>
   <si>
+    <t>meer dan 8.5</t>
+  </si>
+  <si>
     <t>meer dan 2.5</t>
   </si>
   <si>
-    <t>meer dan 8.5</t>
-  </si>
-  <si>
     <t>meer dan 10.5</t>
   </si>
   <si>
@@ -100,18 +103,21 @@
     <t>meer dan 7.5</t>
   </si>
   <si>
+    <t>meer dan 11.5</t>
+  </si>
+  <si>
     <t>toto</t>
   </si>
   <si>
     <t>minder dan 9.5</t>
   </si>
   <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
     <t>minder dan 2.5</t>
   </si>
   <si>
-    <t>minder dan 8.5</t>
-  </si>
-  <si>
     <t>minder dan 10.5</t>
   </si>
   <si>
@@ -121,9 +127,15 @@
     <t>minder dan 7.5</t>
   </si>
   <si>
+    <t>minder dan 11.5</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
+    <t>kambi</t>
+  </si>
+  <si>
     <t>starcasino</t>
   </si>
   <si>
@@ -133,12 +145,12 @@
     <t>1=61, 2=89</t>
   </si>
   <si>
+    <t>1=82, 2=68</t>
+  </si>
+  <si>
     <t>1=59, 2=91</t>
   </si>
   <si>
-    <t>1=82, 2=68</t>
-  </si>
-  <si>
     <t>1=62, 2=88</t>
   </si>
   <si>
@@ -157,6 +169,9 @@
     <t>€5.55</t>
   </si>
   <si>
+    <t>€5.8</t>
+  </si>
+  <si>
     <t>€5.61</t>
   </si>
   <si>
@@ -178,6 +193,9 @@
     <t>€1.2</t>
   </si>
   <si>
+    <t>€1.67</t>
+  </si>
+  <si>
     <t>€2.19</t>
   </si>
   <si>
@@ -196,13 +214,25 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8668833</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.28%7Creplace</t>
+  </si>
+  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344734%7C3.15%7Creplace</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549445</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -576,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -633,43 +663,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>2.55</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I3">
         <v>1.77</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L3">
         <v>4.29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -677,43 +707,43 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I4">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L4">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -721,131 +751,131 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I5">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L5">
-        <v>3.51</v>
+        <v>3.78</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6">
-        <v>3.18</v>
+        <v>3.51</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L7">
-        <v>2.52</v>
+        <v>3.18</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -853,7 +883,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -862,78 +892,78 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L8">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I9">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L9">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -941,175 +971,307 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>1.5</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L10">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11">
+        <v>1.74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11">
         <v>1.71</v>
       </c>
-      <c r="J11" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11">
-        <v>1.52</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I12">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L12">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>2.6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13">
+        <v>1.6667</v>
+      </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13">
+        <v>1.54</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <v>2.5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14">
+        <v>1.71</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14">
+        <v>1.52</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D15" t="s">
         <v>28</v>
       </c>
-      <c r="F13">
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>1.85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15">
+        <v>2.25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
         <v>3.5</v>
       </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13">
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16">
         <v>1.43</v>
       </c>
-      <c r="J13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13">
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16">
         <v>1.5</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>62</v>
+      <c r="M16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1123,19 +1285,25 @@
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10" location="event/1023224918"/>
+    <hyperlink ref="N7" r:id="rId10"/>
     <hyperlink ref="M8" r:id="rId11"/>
     <hyperlink ref="N8" r:id="rId12" location="event/1023224918"/>
     <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
+    <hyperlink ref="N9" r:id="rId14" location="event/1023224918"/>
     <hyperlink ref="M10" r:id="rId15"/>
     <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
     <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18" location="/event/10028349"/>
+    <hyperlink ref="N11" r:id="rId18" location="event/1023224945"/>
     <hyperlink ref="M12" r:id="rId19"/>
-    <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
+    <hyperlink ref="N12" r:id="rId20"/>
     <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22" location="event/1023224945"/>
+    <hyperlink ref="N13" r:id="rId22"/>
+    <hyperlink ref="M14" r:id="rId23"/>
+    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
+    <hyperlink ref="M15" r:id="rId25"/>
+    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
+    <hyperlink ref="M16" r:id="rId27"/>
+    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="94">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,10 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:48:36</t>
+    <t>Laatst bijgewerkt: 2025-09-06 17:54:41</t>
+  </si>
+  <si>
+    <t>Litouwen vs Nederland</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -67,15 +70,18 @@
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
-    <t>Litouwen vs Nederland</t>
-  </si>
-  <si>
     <t>Engeland vs Andorra</t>
   </si>
   <si>
+    <t>totaal aantal schoten</t>
+  </si>
+  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
+    <t>sem steijn</t>
+  </si>
+  <si>
     <t>wedstrijd</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>nederland</t>
   </si>
   <si>
+    <t>meer dan 4.5</t>
+  </si>
+  <si>
     <t>meer dan 9.5</t>
   </si>
   <si>
@@ -97,6 +106,12 @@
     <t>meer dan 10.5</t>
   </si>
   <si>
+    <t>meer dan 5.5</t>
+  </si>
+  <si>
+    <t>meer dan 3.5</t>
+  </si>
+  <si>
     <t>meer dan 1.5</t>
   </si>
   <si>
@@ -106,9 +121,18 @@
     <t>meer dan 11.5</t>
   </si>
   <si>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
+    <t>vbet</t>
+  </si>
+  <si>
     <t>toto</t>
   </si>
   <si>
+    <t>minder dan 4.5</t>
+  </si>
+  <si>
     <t>minder dan 9.5</t>
   </si>
   <si>
@@ -121,6 +145,12 @@
     <t>minder dan 10.5</t>
   </si>
   <si>
+    <t>minder dan 5.5</t>
+  </si>
+  <si>
+    <t>minder dan 3.5</t>
+  </si>
+  <si>
     <t>minder dan 1.5</t>
   </si>
   <si>
@@ -130,6 +160,9 @@
     <t>minder dan 11.5</t>
   </si>
   <si>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
@@ -142,6 +175,9 @@
     <t>onecasino</t>
   </si>
   <si>
+    <t>1=52, 2=98</t>
+  </si>
+  <si>
     <t>1=61, 2=89</t>
   </si>
   <si>
@@ -154,6 +190,12 @@
     <t>1=62, 2=88</t>
   </si>
   <si>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
     <t>1=45, 2=105</t>
   </si>
   <si>
@@ -163,9 +205,15 @@
     <t>1=102, 2=48</t>
   </si>
   <si>
+    <t>1=15, 2=135</t>
+  </si>
+  <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
+    <t>€6.0</t>
+  </si>
+  <si>
     <t>€5.55</t>
   </si>
   <si>
@@ -181,6 +229,12 @@
     <t>€4.88</t>
   </si>
   <si>
+    <t>€4.7</t>
+  </si>
+  <si>
+    <t>€3.87</t>
+  </si>
+  <si>
     <t>€3.3</t>
   </si>
   <si>
@@ -199,12 +253,18 @@
     <t>€2.19</t>
   </si>
   <si>
+    <t>€0.0</t>
+  </si>
+  <si>
     <t>€1.7</t>
   </si>
   <si>
     <t>€1.58</t>
   </si>
   <si>
+    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
+  </si>
+  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
   </si>
   <si>
@@ -217,6 +277,9 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8668833</t>
   </si>
   <si>
+    <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
   </si>
   <si>
@@ -224,9 +287,6 @@
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
-  </si>
-  <si>
-    <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344734%7C3.15%7Creplace</t>
@@ -606,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -666,172 +726,172 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I3">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="L3">
-        <v>4.29</v>
+        <v>4.55</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="L4">
-        <v>3.89</v>
+        <v>4.29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I5">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="L5">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I6">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="L6">
-        <v>3.51</v>
+        <v>3.78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -839,87 +899,87 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I7">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="L7">
-        <v>3.18</v>
+        <v>3.51</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I8">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="L8">
-        <v>2.52</v>
+        <v>3.18</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -933,37 +993,37 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="L9">
-        <v>2.15</v>
+        <v>3.08</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -974,336 +1034,520 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I10">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="L10">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I11">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="L11">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="L12">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I13">
-        <v>1.6667</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L13">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I14">
+        <v>1.74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14">
         <v>1.71</v>
       </c>
-      <c r="J14" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14">
-        <v>1.52</v>
-      </c>
       <c r="M14" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I15">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="L15">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F16">
+        <v>2.6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16">
+        <v>1.6667</v>
+      </c>
+      <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16">
+        <v>1.54</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17">
+        <v>2.5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17">
+        <v>1.71</v>
+      </c>
+      <c r="J17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17">
+        <v>1.52</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18">
+        <v>1.13</v>
+      </c>
+      <c r="J18" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18">
+        <v>1.5</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19">
+        <v>1.85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19">
+        <v>2.25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20">
         <v>3.5</v>
       </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16">
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20">
         <v>1.43</v>
       </c>
-      <c r="J16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16">
+      <c r="J20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" t="s">
+        <v>81</v>
+      </c>
+      <c r="L20">
         <v>1.5</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>70</v>
+      <c r="M20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
     <hyperlink ref="M4" r:id="rId3"/>
     <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
     <hyperlink ref="M5" r:id="rId5"/>
     <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
     <hyperlink ref="M6" r:id="rId7"/>
-    <hyperlink ref="N6" r:id="rId8"/>
+    <hyperlink ref="N6" r:id="rId8" location="event/1023224918"/>
     <hyperlink ref="M7" r:id="rId9"/>
     <hyperlink ref="N7" r:id="rId10"/>
     <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12" location="event/1023224918"/>
+    <hyperlink ref="N8" r:id="rId12"/>
     <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14" location="event/1023224918"/>
+    <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
+    <hyperlink ref="N10" r:id="rId16" location="event/1023224945"/>
     <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18" location="event/1023224945"/>
+    <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
     <hyperlink ref="M12" r:id="rId19"/>
-    <hyperlink ref="N12" r:id="rId20"/>
+    <hyperlink ref="N12" r:id="rId20" location="event/1023224918"/>
     <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22"/>
+    <hyperlink ref="N13" r:id="rId22" location="event/1023224918"/>
     <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
+    <hyperlink ref="N14" r:id="rId24" location="event/1023224945"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
+    <hyperlink ref="N15" r:id="rId26"/>
     <hyperlink ref="M16" r:id="rId27"/>
-    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
+    <hyperlink ref="N16" r:id="rId28"/>
+    <hyperlink ref="M17" r:id="rId29"/>
+    <hyperlink ref="N17" r:id="rId30" location="/event/10028349"/>
+    <hyperlink ref="M18" r:id="rId31"/>
+    <hyperlink ref="N18" r:id="rId32" location="event/1023224945"/>
+    <hyperlink ref="M19" r:id="rId33"/>
+    <hyperlink ref="N19" r:id="rId34" location="event/1023224945"/>
+    <hyperlink ref="M20" r:id="rId35"/>
+    <hyperlink ref="N20" r:id="rId36" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="89">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,45 +58,45 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 17:54:41</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:01:25</t>
+  </si>
+  <si>
+    <t>Armenië vs Portugal</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
-    <t>Armenië vs Portugal</t>
-  </si>
-  <si>
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
     <t>Engeland vs Andorra</t>
   </si>
   <si>
+    <t>totaal aantal schoten op doel</t>
+  </si>
+  <si>
     <t>totaal aantal schoten</t>
   </si>
   <si>
-    <t>totaal aantal schoten op doel</t>
+    <t>wedstrijd</t>
   </si>
   <si>
     <t>sem steijn</t>
   </si>
   <si>
-    <t>wedstrijd</t>
-  </si>
-  <si>
     <t>armenië</t>
   </si>
   <si>
     <t>nederland</t>
   </si>
   <si>
+    <t>meer dan 9.5</t>
+  </si>
+  <si>
     <t>meer dan 4.5</t>
   </si>
   <si>
-    <t>meer dan 9.5</t>
-  </si>
-  <si>
     <t>meer dan 8.5</t>
   </si>
   <si>
@@ -112,30 +112,30 @@
     <t>meer dan 3.5</t>
   </si>
   <si>
+    <t>meer dan 7.5</t>
+  </si>
+  <si>
     <t>meer dan 1.5</t>
   </si>
   <si>
-    <t>meer dan 7.5</t>
-  </si>
-  <si>
     <t>meer dan 11.5</t>
   </si>
   <si>
     <t>meer dan 6.5</t>
   </si>
   <si>
+    <t>toto</t>
+  </si>
+  <si>
     <t>vbet</t>
   </si>
   <si>
-    <t>toto</t>
+    <t>minder dan 9.5</t>
   </si>
   <si>
     <t>minder dan 4.5</t>
   </si>
   <si>
-    <t>minder dan 9.5</t>
-  </si>
-  <si>
     <t>minder dan 8.5</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>minder dan 3.5</t>
   </si>
   <si>
+    <t>minder dan 7.5</t>
+  </si>
+  <si>
     <t>minder dan 1.5</t>
   </si>
   <si>
-    <t>minder dan 7.5</t>
-  </si>
-  <si>
     <t>minder dan 11.5</t>
   </si>
   <si>
@@ -166,66 +166,60 @@
     <t>jacks</t>
   </si>
   <si>
-    <t>kambi</t>
-  </si>
-  <si>
     <t>starcasino</t>
   </si>
   <si>
     <t>onecasino</t>
   </si>
   <si>
+    <t>1=62, 2=88</t>
+  </si>
+  <si>
     <t>1=52, 2=98</t>
   </si>
   <si>
+    <t>1=82, 2=68</t>
+  </si>
+  <si>
+    <t>1=59, 2=91</t>
+  </si>
+  <si>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
+    <t>1=45, 2=105</t>
+  </si>
+  <si>
+    <t>1=102, 2=48</t>
+  </si>
+  <si>
+    <t>1=98, 2=52</t>
+  </si>
+  <si>
     <t>1=61, 2=89</t>
   </si>
   <si>
-    <t>1=82, 2=68</t>
-  </si>
-  <si>
-    <t>1=59, 2=91</t>
-  </si>
-  <si>
-    <t>1=62, 2=88</t>
-  </si>
-  <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
-    <t>1=45, 2=105</t>
-  </si>
-  <si>
-    <t>1=99, 2=51</t>
-  </si>
-  <si>
-    <t>1=102, 2=48</t>
-  </si>
-  <si>
     <t>1=15, 2=135</t>
   </si>
   <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
+    <t>€6.64</t>
+  </si>
+  <si>
     <t>€6.0</t>
   </si>
   <si>
-    <t>€5.55</t>
-  </si>
-  <si>
     <t>€5.8</t>
   </si>
   <si>
     <t>€5.61</t>
   </si>
   <si>
-    <t>€5.04</t>
-  </si>
-  <si>
     <t>€4.88</t>
   </si>
   <si>
@@ -244,9 +238,6 @@
     <t>€1.9</t>
   </si>
   <si>
-    <t>€1.2</t>
-  </si>
-  <si>
     <t>€1.67</t>
   </si>
   <si>
@@ -262,12 +253,12 @@
     <t>€1.58</t>
   </si>
   <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
+  </si>
+  <si>
     <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
-  </si>
-  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
   </si>
   <si>
@@ -277,19 +268,13 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8668833</t>
   </si>
   <si>
+    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.28%7Creplace</t>
-  </si>
-  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344734%7C3.15%7Creplace</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549445</t>
@@ -666,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -735,7 +720,7 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="G3" t="s">
         <v>38</v>
@@ -744,22 +729,22 @@
         <v>49</v>
       </c>
       <c r="I3">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L3">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -779,7 +764,7 @@
         <v>37</v>
       </c>
       <c r="F4">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="G4" t="s">
         <v>39</v>
@@ -788,39 +773,39 @@
         <v>49</v>
       </c>
       <c r="I4">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L4">
-        <v>4.29</v>
+        <v>4.55</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>1.9</v>
@@ -835,27 +820,27 @@
         <v>2.3</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L5">
         <v>3.89</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -864,7 +849,7 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>2.65</v>
@@ -879,68 +864,68 @@
         <v>1.71</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L6">
         <v>3.78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
         <v>50</v>
       </c>
       <c r="I7">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L7">
-        <v>3.51</v>
+        <v>3.18</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
@@ -949,81 +934,81 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
       </c>
       <c r="F8">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
         <v>49</v>
       </c>
       <c r="I9">
-        <v>1.3</v>
+        <v>2.23</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L9">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1037,81 +1022,81 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
       </c>
       <c r="F10">
-        <v>1.91</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
         <v>49</v>
       </c>
       <c r="I10">
-        <v>2.23</v>
+        <v>1.46</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L10">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>3.45</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
         <v>49</v>
       </c>
       <c r="I11">
-        <v>1.46</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L11">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1119,63 +1104,63 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L12">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G13" t="s">
         <v>46</v>
@@ -1184,63 +1169,63 @@
         <v>49</v>
       </c>
       <c r="I13">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L13">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14">
-        <v>1.74</v>
+        <v>1.6667</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L14">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>87</v>
@@ -1248,51 +1233,51 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L15">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
@@ -1301,116 +1286,116 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
       </c>
       <c r="F16">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I16">
-        <v>1.6667</v>
+        <v>1.13</v>
       </c>
       <c r="J16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L16">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I17">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="J17" t="s">
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L17">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
         <v>36</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
         <v>49</v>
       </c>
       <c r="I18">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="J18" t="s">
         <v>63</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L18">
         <v>1.5</v>
@@ -1419,103 +1404,15 @@
         <v>82</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19">
-        <v>1.85</v>
-      </c>
-      <c r="G19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19">
-        <v>2.25</v>
-      </c>
-      <c r="J19" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" t="s">
-        <v>80</v>
-      </c>
-      <c r="L19">
-        <v>1.5</v>
-      </c>
-      <c r="M19" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20">
-        <v>3.5</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20">
-        <v>1.43</v>
-      </c>
-      <c r="J20" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20">
-        <v>1.5</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
     <hyperlink ref="M4" r:id="rId3"/>
-    <hyperlink ref="N4" r:id="rId4" location="event/1023224918"/>
+    <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>
     <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
     <hyperlink ref="M6" r:id="rId7"/>
@@ -1523,31 +1420,27 @@
     <hyperlink ref="M7" r:id="rId9"/>
     <hyperlink ref="N7" r:id="rId10"/>
     <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12"/>
+    <hyperlink ref="N8" r:id="rId12" location="event/1023224945"/>
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16" location="event/1023224945"/>
+    <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
     <hyperlink ref="M11" r:id="rId17"/>
     <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
     <hyperlink ref="M12" r:id="rId19"/>
-    <hyperlink ref="N12" r:id="rId20" location="event/1023224918"/>
+    <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
     <hyperlink ref="M13" r:id="rId21"/>
     <hyperlink ref="N13" r:id="rId22" location="event/1023224918"/>
     <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24" location="event/1023224945"/>
+    <hyperlink ref="N14" r:id="rId24"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26"/>
+    <hyperlink ref="N15" r:id="rId26" location="/event/10028349"/>
     <hyperlink ref="M16" r:id="rId27"/>
-    <hyperlink ref="N16" r:id="rId28"/>
+    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
     <hyperlink ref="M17" r:id="rId29"/>
-    <hyperlink ref="N17" r:id="rId30" location="/event/10028349"/>
+    <hyperlink ref="N17" r:id="rId30" location="event/1023224945"/>
     <hyperlink ref="M18" r:id="rId31"/>
     <hyperlink ref="N18" r:id="rId32" location="event/1023224945"/>
-    <hyperlink ref="M19" r:id="rId33"/>
-    <hyperlink ref="N19" r:id="rId34" location="event/1023224945"/>
-    <hyperlink ref="M20" r:id="rId35"/>
-    <hyperlink ref="N20" r:id="rId36" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:01:25</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:06:23</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -163,6 +163,9 @@
     <t>minder dan 6.5</t>
   </si>
   <si>
+    <t>kambi</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
@@ -268,13 +271,28 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8668833</t>
   </si>
   <si>
-    <t>https://jacks.nl/sports/event/1023224918#event/1023224918</t>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.78%7Creplace</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.30%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.71%7Creplace</t>
+  </si>
+  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.46%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344734%7C3.20%7Creplace</t>
+  </si>
+  <si>
+    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344782%7C2.95%7Creplace</t>
   </si>
   <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549445</t>
@@ -732,19 +750,19 @@
         <v>1.78</v>
       </c>
       <c r="J3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L3">
         <v>4.6</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -770,25 +788,25 @@
         <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <v>1.61</v>
       </c>
       <c r="J4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L4">
         <v>4.55</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -820,19 +838,19 @@
         <v>2.3</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5">
         <v>3.89</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -864,19 +882,19 @@
         <v>1.71</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6">
         <v>3.78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -902,25 +920,25 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7">
         <v>1.76</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L7">
         <v>3.18</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -946,25 +964,25 @@
         <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8">
         <v>1.3</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8">
         <v>3.08</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -990,25 +1008,25 @@
         <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I9">
         <v>2.23</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L9">
         <v>2.8</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1040,19 +1058,19 @@
         <v>1.46</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L10">
         <v>2.52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1084,19 +1102,19 @@
         <v>3.2</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L11">
         <v>2.08</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1122,25 +1140,25 @@
         <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I12">
         <v>1.74</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L12">
         <v>1.71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1172,19 +1190,19 @@
         <v>2.95</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L13">
         <v>1.59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1210,25 +1228,25 @@
         <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I14">
         <v>1.6667</v>
       </c>
       <c r="J14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L14">
         <v>1.54</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1254,25 +1272,25 @@
         <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15">
         <v>1.71</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L15">
         <v>1.52</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1298,25 +1316,25 @@
         <v>48</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I16">
         <v>1.13</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L16">
         <v>1.5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1342,25 +1360,25 @@
         <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17">
         <v>2.25</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L17">
         <v>1.5</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1386,37 +1404,37 @@
         <v>38</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18">
         <v>1.43</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L18">
         <v>1.5</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224918"/>
+    <hyperlink ref="N3" r:id="rId2"/>
     <hyperlink ref="M4" r:id="rId3"/>
     <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6" location="event/1023224918"/>
+    <hyperlink ref="N5" r:id="rId6"/>
     <hyperlink ref="M6" r:id="rId7"/>
-    <hyperlink ref="N6" r:id="rId8" location="event/1023224918"/>
+    <hyperlink ref="N6" r:id="rId8"/>
     <hyperlink ref="M7" r:id="rId9"/>
     <hyperlink ref="N7" r:id="rId10"/>
     <hyperlink ref="M8" r:id="rId11"/>
@@ -1424,13 +1442,13 @@
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16" location="event/1023224918"/>
+    <hyperlink ref="N10" r:id="rId16"/>
     <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18" location="event/1023224918"/>
+    <hyperlink ref="N11" r:id="rId18"/>
     <hyperlink ref="M12" r:id="rId19"/>
     <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
     <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22" location="event/1023224918"/>
+    <hyperlink ref="N13" r:id="rId22"/>
     <hyperlink ref="M14" r:id="rId23"/>
     <hyperlink ref="N14" r:id="rId24"/>
     <hyperlink ref="M15" r:id="rId25"/>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:06:23</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:13:48</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>
@@ -70,9 +70,6 @@
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
-    <t>Engeland vs Andorra</t>
-  </si>
-  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>meer dan 1.5</t>
   </si>
   <si>
-    <t>meer dan 11.5</t>
-  </si>
-  <si>
     <t>meer dan 6.5</t>
   </si>
   <si>
@@ -157,9 +151,6 @@
     <t>minder dan 1.5</t>
   </si>
   <si>
-    <t>minder dan 11.5</t>
-  </si>
-  <si>
     <t>minder dan 6.5</t>
   </si>
   <si>
@@ -241,9 +232,6 @@
     <t>€1.9</t>
   </si>
   <si>
-    <t>€1.67</t>
-  </si>
-  <si>
     <t>€2.19</t>
   </si>
   <si>
@@ -268,9 +256,6 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8668833</t>
-  </si>
-  <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.78%7Creplace</t>
   </si>
   <si>
@@ -293,9 +278,6 @@
   </si>
   <si>
     <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344782%7C2.95%7Creplace</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=13549445</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -669,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -726,43 +708,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>2.55</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I3">
         <v>1.78</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L3">
         <v>4.6</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -770,43 +752,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I4">
         <v>1.61</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L4">
         <v>4.55</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -814,43 +796,43 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>1.9</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I5">
         <v>2.3</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L5">
         <v>3.89</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -858,43 +840,43 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>2.65</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>1.71</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L6">
         <v>3.78</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -902,43 +884,43 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>2.5</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I7">
         <v>1.76</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L7">
         <v>3.18</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -946,43 +928,43 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8">
         <v>1.3</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L8">
         <v>3.08</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -990,43 +972,43 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>1.91</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I9">
         <v>2.23</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L9">
         <v>2.8</v>
       </c>
       <c r="M9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1034,43 +1016,43 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>3.45</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I10">
         <v>1.46</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L10">
         <v>2.52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1078,43 +1060,43 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>1.5</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I11">
         <v>3.2</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L11">
         <v>2.08</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1122,43 +1104,43 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>2.45</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I12">
         <v>1.74</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L12">
         <v>1.71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1166,92 +1148,92 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>1.55</v>
       </c>
       <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
         <v>46</v>
-      </c>
-      <c r="H13" t="s">
-        <v>49</v>
       </c>
       <c r="I13">
         <v>2.95</v>
       </c>
       <c r="J13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L13">
         <v>1.59</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
       <c r="F14">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I14">
-        <v>1.6667</v>
+        <v>1.71</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L14">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -1260,37 +1242,37 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I15">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L15">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1298,43 +1280,43 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I16">
-        <v>1.13</v>
+        <v>2.25</v>
       </c>
       <c r="J16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L16">
         <v>1.5</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1342,87 +1324,43 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
       <c r="E17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17">
+        <v>3.5</v>
+      </c>
+      <c r="G17" t="s">
         <v>36</v>
       </c>
-      <c r="F17">
-        <v>1.85</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
-      </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I17">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="J17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L17">
         <v>1.5</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18">
-        <v>3.5</v>
-      </c>
-      <c r="G18" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18">
-        <v>1.43</v>
-      </c>
-      <c r="J18" t="s">
-        <v>64</v>
-      </c>
-      <c r="K18" t="s">
-        <v>79</v>
-      </c>
-      <c r="L18">
-        <v>1.5</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1450,15 +1388,13 @@
     <hyperlink ref="M13" r:id="rId21"/>
     <hyperlink ref="N13" r:id="rId22"/>
     <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24"/>
+    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
     <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="/event/10028349"/>
+    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
     <hyperlink ref="M16" r:id="rId27"/>
     <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
     <hyperlink ref="M17" r:id="rId29"/>
     <hyperlink ref="N17" r:id="rId30" location="event/1023224945"/>
-    <hyperlink ref="M18" r:id="rId31"/>
-    <hyperlink ref="N18" r:id="rId32" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:13:48</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:17:30</t>
   </si>
   <si>
     <t>Armenië vs Portugal</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,10 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:17:30</t>
-  </si>
-  <si>
-    <t>Armenië vs Portugal</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:21:40</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
@@ -70,93 +67,75 @@
     <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
+    <t>totaal aantal schoten</t>
+  </si>
+  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
-    <t>totaal aantal schoten</t>
+    <t>sem steijn</t>
   </si>
   <si>
     <t>wedstrijd</t>
   </si>
   <si>
-    <t>sem steijn</t>
-  </si>
-  <si>
-    <t>armenië</t>
-  </si>
-  <si>
     <t>nederland</t>
   </si>
   <si>
+    <t>meer dan 4.5</t>
+  </si>
+  <si>
+    <t>meer dan 10.5</t>
+  </si>
+  <si>
+    <t>meer dan 5.5</t>
+  </si>
+  <si>
+    <t>meer dan 3.5</t>
+  </si>
+  <si>
+    <t>meer dan 8.5</t>
+  </si>
+  <si>
+    <t>meer dan 6.5</t>
+  </si>
+  <si>
+    <t>meer dan 7.5</t>
+  </si>
+  <si>
     <t>meer dan 9.5</t>
   </si>
   <si>
-    <t>meer dan 4.5</t>
-  </si>
-  <si>
-    <t>meer dan 8.5</t>
-  </si>
-  <si>
-    <t>meer dan 2.5</t>
-  </si>
-  <si>
-    <t>meer dan 10.5</t>
-  </si>
-  <si>
-    <t>meer dan 5.5</t>
-  </si>
-  <si>
-    <t>meer dan 3.5</t>
-  </si>
-  <si>
-    <t>meer dan 7.5</t>
-  </si>
-  <si>
-    <t>meer dan 1.5</t>
-  </si>
-  <si>
-    <t>meer dan 6.5</t>
+    <t>vbet</t>
   </si>
   <si>
     <t>toto</t>
   </si>
   <si>
-    <t>vbet</t>
+    <t>minder dan 4.5</t>
+  </si>
+  <si>
+    <t>minder dan 10.5</t>
+  </si>
+  <si>
+    <t>minder dan 5.5</t>
+  </si>
+  <si>
+    <t>minder dan 3.5</t>
+  </si>
+  <si>
+    <t>minder dan 8.5</t>
+  </si>
+  <si>
+    <t>minder dan 6.5</t>
+  </si>
+  <si>
+    <t>minder dan 7.5</t>
   </si>
   <si>
     <t>minder dan 9.5</t>
   </si>
   <si>
-    <t>minder dan 4.5</t>
-  </si>
-  <si>
-    <t>minder dan 8.5</t>
-  </si>
-  <si>
-    <t>minder dan 2.5</t>
-  </si>
-  <si>
-    <t>minder dan 10.5</t>
-  </si>
-  <si>
-    <t>minder dan 5.5</t>
-  </si>
-  <si>
-    <t>minder dan 3.5</t>
-  </si>
-  <si>
-    <t>minder dan 7.5</t>
-  </si>
-  <si>
-    <t>minder dan 1.5</t>
-  </si>
-  <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
-    <t>kambi</t>
-  </si>
-  <si>
     <t>jacks</t>
   </si>
   <si>
@@ -166,54 +145,33 @@
     <t>onecasino</t>
   </si>
   <si>
+    <t>1=52, 2=98</t>
+  </si>
+  <si>
     <t>1=62, 2=88</t>
   </si>
   <si>
-    <t>1=52, 2=98</t>
+    <t>1=31, 2=119</t>
+  </si>
+  <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
+    <t>1=61, 2=89</t>
+  </si>
+  <si>
+    <t>1=15, 2=135</t>
   </si>
   <si>
     <t>1=82, 2=68</t>
   </si>
   <si>
-    <t>1=59, 2=91</t>
-  </si>
-  <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
-    <t>1=45, 2=105</t>
-  </si>
-  <si>
-    <t>1=102, 2=48</t>
-  </si>
-  <si>
-    <t>1=98, 2=52</t>
-  </si>
-  <si>
-    <t>1=61, 2=89</t>
-  </si>
-  <si>
-    <t>1=15, 2=135</t>
-  </si>
-  <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
-    <t>€6.64</t>
-  </si>
-  <si>
     <t>€6.0</t>
   </si>
   <si>
-    <t>€5.8</t>
-  </si>
-  <si>
-    <t>€5.61</t>
-  </si>
-  <si>
     <t>€4.88</t>
   </si>
   <si>
@@ -223,12 +181,6 @@
     <t>€3.87</t>
   </si>
   <si>
-    <t>€3.3</t>
-  </si>
-  <si>
-    <t>€3.0</t>
-  </si>
-  <si>
     <t>€1.9</t>
   </si>
   <si>
@@ -244,9 +196,6 @@
     <t>€1.58</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8590793</t>
-  </si>
-  <si>
     <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
@@ -256,28 +205,10 @@
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344853%7C1.78%7Creplace</t>
-  </si>
-  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
   </si>
   <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344817%7C2.30%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344897%7C1.71%7Creplace</t>
-  </si>
-  <si>
     <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344793%7C1.46%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344734%7C3.20%7Creplace</t>
-  </si>
-  <si>
-    <t>https://www.unibet.nl/betting/sports/event/1023224918?coupon=single%7C3856344782%7C2.95%7Creplace</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -651,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -708,43 +639,43 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="J3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="L3">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -752,43 +683,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I4">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L4">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -796,43 +727,43 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="F5">
-        <v>1.9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L5">
-        <v>3.89</v>
+        <v>3.08</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -840,87 +771,87 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>2.23</v>
+      </c>
+      <c r="J6" t="s">
         <v>46</v>
       </c>
-      <c r="I6">
-        <v>1.71</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L6">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
         <v>40</v>
       </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
       <c r="I7">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="L7">
-        <v>3.18</v>
+        <v>1.71</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -928,87 +859,87 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8">
+        <v>1.71</v>
+      </c>
+      <c r="J8" t="s">
         <v>47</v>
       </c>
-      <c r="I8">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="s">
-        <v>54</v>
-      </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="L8">
-        <v>3.08</v>
+        <v>1.52</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
       <c r="F9">
-        <v>1.91</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>2.23</v>
+        <v>1.13</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L9">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1019,40 +950,40 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
         <v>40</v>
       </c>
-      <c r="H10" t="s">
-        <v>46</v>
-      </c>
       <c r="I10">
-        <v>1.46</v>
+        <v>2.25</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L10">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1063,338 +994,62 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
       <c r="F11">
+        <v>3.5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11">
+        <v>1.43</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11">
         <v>1.5</v>
       </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11">
-        <v>3.2</v>
-      </c>
-      <c r="J11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11">
-        <v>2.08</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12">
-        <v>2.45</v>
-      </c>
-      <c r="G12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12">
-        <v>1.74</v>
-      </c>
-      <c r="J12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12">
-        <v>1.71</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13">
-        <v>1.55</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13">
-        <v>2.95</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13">
-        <v>1.59</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14">
-        <v>2.5</v>
-      </c>
-      <c r="G14" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14">
-        <v>1.71</v>
-      </c>
-      <c r="J14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14">
-        <v>1.52</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-      <c r="G15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15">
-        <v>1.13</v>
-      </c>
-      <c r="J15" t="s">
-        <v>60</v>
-      </c>
-      <c r="K15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L15">
-        <v>1.5</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16">
-        <v>1.85</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16">
-        <v>2.25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" t="s">
-        <v>74</v>
-      </c>
-      <c r="L16">
-        <v>1.5</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17">
-        <v>3.5</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17">
-        <v>1.43</v>
-      </c>
-      <c r="J17" t="s">
-        <v>61</v>
-      </c>
-      <c r="K17" t="s">
-        <v>75</v>
-      </c>
-      <c r="L17">
-        <v>1.5</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
     <hyperlink ref="M4" r:id="rId3"/>
-    <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
+    <hyperlink ref="N4" r:id="rId4"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6"/>
+    <hyperlink ref="N5" r:id="rId6" location="event/1023224945"/>
     <hyperlink ref="M6" r:id="rId7"/>
-    <hyperlink ref="N6" r:id="rId8"/>
+    <hyperlink ref="N6" r:id="rId8" location="event/1023224945"/>
     <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224945"/>
     <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12" location="event/1023224945"/>
+    <hyperlink ref="N8" r:id="rId12" location="/event/10028349"/>
     <hyperlink ref="M9" r:id="rId13"/>
     <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
     <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16"/>
+    <hyperlink ref="N10" r:id="rId16" location="event/1023224945"/>
     <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18"/>
-    <hyperlink ref="M12" r:id="rId19"/>
-    <hyperlink ref="N12" r:id="rId20" location="event/1023224945"/>
-    <hyperlink ref="M13" r:id="rId21"/>
-    <hyperlink ref="N13" r:id="rId22"/>
-    <hyperlink ref="M14" r:id="rId23"/>
-    <hyperlink ref="N14" r:id="rId24" location="/event/10028349"/>
-    <hyperlink ref="M15" r:id="rId25"/>
-    <hyperlink ref="N15" r:id="rId26" location="event/1023224945"/>
-    <hyperlink ref="M16" r:id="rId27"/>
-    <hyperlink ref="N16" r:id="rId28" location="event/1023224945"/>
-    <hyperlink ref="M17" r:id="rId29"/>
-    <hyperlink ref="N17" r:id="rId30" location="event/1023224945"/>
+    <hyperlink ref="N11" r:id="rId18" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:21:40</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:26:38</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:26:38</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:32:12</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:32:12</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:38:37</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,157 +58,97 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:38:37</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:43:52</t>
+  </si>
+  <si>
+    <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
-    <t>Duitsland vs Noord-Ierland</t>
-  </si>
-  <si>
-    <t>totaal aantal schoten</t>
-  </si>
-  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
-    <t>sem steijn</t>
-  </si>
-  <si>
     <t>wedstrijd</t>
   </si>
   <si>
     <t>nederland</t>
   </si>
   <si>
-    <t>meer dan 4.5</t>
-  </si>
-  <si>
     <t>meer dan 10.5</t>
   </si>
   <si>
-    <t>meer dan 5.5</t>
-  </si>
-  <si>
-    <t>meer dan 3.5</t>
-  </si>
-  <si>
     <t>meer dan 8.5</t>
   </si>
   <si>
-    <t>meer dan 6.5</t>
-  </si>
-  <si>
     <t>meer dan 7.5</t>
   </si>
   <si>
     <t>meer dan 9.5</t>
   </si>
   <si>
-    <t>vbet</t>
-  </si>
-  <si>
     <t>toto</t>
   </si>
   <si>
-    <t>minder dan 4.5</t>
-  </si>
-  <si>
     <t>minder dan 10.5</t>
   </si>
   <si>
-    <t>minder dan 5.5</t>
-  </si>
-  <si>
-    <t>minder dan 3.5</t>
-  </si>
-  <si>
     <t>minder dan 8.5</t>
   </si>
   <si>
-    <t>minder dan 6.5</t>
-  </si>
-  <si>
     <t>minder dan 7.5</t>
   </si>
   <si>
     <t>minder dan 9.5</t>
   </si>
   <si>
+    <t>starcasino</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
-    <t>starcasino</t>
-  </si>
-  <si>
     <t>onecasino</t>
   </si>
   <si>
-    <t>1=52, 2=98</t>
-  </si>
-  <si>
     <t>1=62, 2=88</t>
   </si>
   <si>
-    <t>1=31, 2=119</t>
-  </si>
-  <si>
-    <t>1=81, 2=69</t>
-  </si>
-  <si>
     <t>1=61, 2=89</t>
   </si>
   <si>
-    <t>1=15, 2=135</t>
-  </si>
-  <si>
     <t>1=82, 2=68</t>
   </si>
   <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
-    <t>€6.0</t>
-  </si>
-  <si>
     <t>€4.88</t>
   </si>
   <si>
-    <t>€4.7</t>
-  </si>
-  <si>
-    <t>€3.87</t>
-  </si>
-  <si>
     <t>€1.9</t>
   </si>
   <si>
     <t>€2.19</t>
   </si>
   <si>
-    <t>€0.0</t>
-  </si>
-  <si>
     <t>€1.7</t>
   </si>
   <si>
     <t>€1.58</t>
   </si>
   <si>
-    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
-  </si>
-  <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
   </si>
   <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
+  </si>
+  <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
     <t>https://sports.onecasino.nl/#/event/10028349</t>
@@ -582,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -642,40 +582,40 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3">
+        <v>1.76</v>
+      </c>
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3">
-        <v>1.61</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3">
+        <v>3.18</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3">
-        <v>4.55</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -683,43 +623,43 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I4">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4">
+        <v>1.71</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4">
-        <v>3.18</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -730,45 +670,45 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
       <c r="F5">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5">
+        <v>1.52</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5">
-        <v>3.08</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -777,279 +717,95 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>1.85</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
         <v>30</v>
       </c>
-      <c r="F6">
-        <v>1.91</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
       <c r="I6">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="L6">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7">
+        <v>1.43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="I7">
-        <v>1.74</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="L7">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7">
-        <v>1.71</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>2.5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8">
-        <v>1.71</v>
-      </c>
-      <c r="J8" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8">
-        <v>1.52</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>1.13</v>
-      </c>
-      <c r="J9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9">
-        <v>1.5</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10">
-        <v>1.85</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10">
-        <v>2.25</v>
-      </c>
-      <c r="J10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10">
-        <v>1.5</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11">
-        <v>3.5</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11">
-        <v>1.43</v>
-      </c>
-      <c r="J11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11">
-        <v>1.5</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
+    <hyperlink ref="N3" r:id="rId2"/>
     <hyperlink ref="M4" r:id="rId3"/>
-    <hyperlink ref="N4" r:id="rId4"/>
+    <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6" location="event/1023224945"/>
+    <hyperlink ref="N5" r:id="rId6" location="/event/10028349"/>
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8" location="event/1023224945"/>
     <hyperlink ref="M7" r:id="rId9"/>
     <hyperlink ref="N7" r:id="rId10" location="event/1023224945"/>
-    <hyperlink ref="M8" r:id="rId11"/>
-    <hyperlink ref="N8" r:id="rId12" location="/event/10028349"/>
-    <hyperlink ref="M9" r:id="rId13"/>
-    <hyperlink ref="N9" r:id="rId14" location="event/1023224945"/>
-    <hyperlink ref="M10" r:id="rId15"/>
-    <hyperlink ref="N10" r:id="rId16" location="event/1023224945"/>
-    <hyperlink ref="M11" r:id="rId17"/>
-    <hyperlink ref="N11" r:id="rId18" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:43:52</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:48:59</t>
   </si>
   <si>
     <t>Duitsland vs Noord-Ierland</t>
@@ -109,15 +109,9 @@
     <t>jacks</t>
   </si>
   <si>
-    <t>onecasino</t>
-  </si>
-  <si>
     <t>1=62, 2=88</t>
   </si>
   <si>
-    <t>1=61, 2=89</t>
-  </si>
-  <si>
     <t>1=82, 2=68</t>
   </si>
   <si>
@@ -130,9 +124,6 @@
     <t>€1.9</t>
   </si>
   <si>
-    <t>€2.19</t>
-  </si>
-  <si>
     <t>€1.7</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
-  </si>
-  <si>
-    <t>https://sports.onecasino.nl/#/event/10028349</t>
   </si>
 </sst>
 </file>
@@ -522,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -603,19 +591,19 @@
         <v>1.76</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L3">
         <v>3.18</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -647,63 +635,63 @@
         <v>1.74</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L4">
         <v>1.71</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
       <c r="F5">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -717,81 +705,37 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
       </c>
       <c r="I6">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L6">
         <v>1.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>3.5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7">
-        <v>1.43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7">
-        <v>1.5</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -801,11 +745,9 @@
     <hyperlink ref="M4" r:id="rId3"/>
     <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>
-    <hyperlink ref="N5" r:id="rId6" location="/event/10028349"/>
+    <hyperlink ref="N5" r:id="rId6" location="event/1023224945"/>
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8" location="event/1023224945"/>
-    <hyperlink ref="M7" r:id="rId9"/>
-    <hyperlink ref="N7" r:id="rId10" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:48:59</t>
+    <t>Laatst bijgewerkt: 2025-09-06 18:54:20</t>
   </si>
   <si>
     <t>Duitsland vs Noord-Ierland</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 18:54:20</t>
+    <t>Laatst bijgewerkt: 2025-09-06 19:04:42</t>
   </si>
   <si>
     <t>Duitsland vs Noord-Ierland</t>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,25 +58,25 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 19:04:42</t>
-  </si>
-  <si>
-    <t>Duitsland vs Noord-Ierland</t>
+    <t>Laatst bijgewerkt: 2025-09-06 19:12:44</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
+    <t>totaal aantal schoten</t>
+  </si>
+  <si>
     <t>totaal aantal schoten op doel</t>
   </si>
   <si>
-    <t>wedstrijd</t>
+    <t>sem steijn</t>
   </si>
   <si>
     <t>nederland</t>
   </si>
   <si>
-    <t>meer dan 10.5</t>
+    <t>meer dan 3.5</t>
   </si>
   <si>
     <t>meer dan 8.5</t>
@@ -88,10 +88,13 @@
     <t>meer dan 9.5</t>
   </si>
   <si>
+    <t>vbet</t>
+  </si>
+  <si>
     <t>toto</t>
   </si>
   <si>
-    <t>minder dan 10.5</t>
+    <t>minder dan 3.5</t>
   </si>
   <si>
     <t>minder dan 8.5</t>
@@ -103,12 +106,12 @@
     <t>minder dan 9.5</t>
   </si>
   <si>
-    <t>starcasino</t>
-  </si>
-  <si>
     <t>jacks</t>
   </si>
   <si>
+    <t>1=81, 2=69</t>
+  </si>
+  <si>
     <t>1=62, 2=88</t>
   </si>
   <si>
@@ -118,7 +121,7 @@
     <t>1=44, 2=106</t>
   </si>
   <si>
-    <t>€4.88</t>
+    <t>€3.87</t>
   </si>
   <si>
     <t>€1.9</t>
@@ -130,13 +133,10 @@
     <t>€1.58</t>
   </si>
   <si>
-    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
+    <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
-  </si>
-  <si>
-    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
@@ -567,7 +567,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -579,36 +579,36 @@
         <v>24</v>
       </c>
       <c r="F3">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -620,13 +620,13 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>2.45</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
         <v>30</v>
@@ -635,16 +635,16 @@
         <v>1.74</v>
       </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4">
         <v>1.71</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>41</v>
@@ -652,7 +652,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -664,13 +664,13 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>1.85</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -679,16 +679,16 @@
         <v>2.25</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5">
         <v>1.5</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>41</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -708,13 +708,13 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>3.5</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
@@ -723,16 +723,16 @@
         <v>1.43</v>
       </c>
       <c r="J6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>1.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>41</v>
@@ -741,7 +741,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
+    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
     <hyperlink ref="M4" r:id="rId3"/>
     <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>Wedstrijd</t>
   </si>
@@ -58,16 +58,22 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 19:12:44</t>
+    <t>Laatst bijgewerkt: 2025-09-06 19:17:39</t>
+  </si>
+  <si>
+    <t>Duitsland vs Noord-Ierland</t>
   </si>
   <si>
     <t>Litouwen vs Nederland</t>
   </si>
   <si>
+    <t>totaal aantal schoten op doel</t>
+  </si>
+  <si>
     <t>totaal aantal schoten</t>
   </si>
   <si>
-    <t>totaal aantal schoten op doel</t>
+    <t>wedstrijd</t>
   </si>
   <si>
     <t>sem steijn</t>
@@ -76,6 +82,9 @@
     <t>nederland</t>
   </si>
   <si>
+    <t>meer dan 10.5</t>
+  </si>
+  <si>
     <t>meer dan 3.5</t>
   </si>
   <si>
@@ -88,10 +97,13 @@
     <t>meer dan 9.5</t>
   </si>
   <si>
+    <t>toto</t>
+  </si>
+  <si>
     <t>vbet</t>
   </si>
   <si>
-    <t>toto</t>
+    <t>minder dan 10.5</t>
   </si>
   <si>
     <t>minder dan 3.5</t>
@@ -106,21 +118,27 @@
     <t>minder dan 9.5</t>
   </si>
   <si>
+    <t>starcasino</t>
+  </si>
+  <si>
     <t>jacks</t>
   </si>
   <si>
+    <t>1=62, 2=88</t>
+  </si>
+  <si>
     <t>1=81, 2=69</t>
   </si>
   <si>
-    <t>1=62, 2=88</t>
-  </si>
-  <si>
     <t>1=82, 2=68</t>
   </si>
   <si>
     <t>1=44, 2=106</t>
   </si>
   <si>
+    <t>€4.88</t>
+  </si>
+  <si>
     <t>€3.87</t>
   </si>
   <si>
@@ -133,10 +151,16 @@
     <t>€1.58</t>
   </si>
   <si>
+    <t>https://sport.toto.nl/wedden/wedstrijd/8778584</t>
+  </si>
+  <si>
     <t>https://www.vbet.nl/nl/sports/pre-match/event-view/Soccer/World/18277589/world-cup-europe-qualification/27857408/litouwen-nederland</t>
   </si>
   <si>
     <t>https://sport.toto.nl/wedden/wedstrijd/8706282</t>
+  </si>
+  <si>
+    <t>https://starcasino.nl/prematch-bets?page=event&amp;sportId=66&amp;eventId=12642394</t>
   </si>
   <si>
     <t>https://jacks.nl/sports/event/1023224945#event/1023224945</t>
@@ -510,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -567,187 +591,233 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L4">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I6">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L6">
         <v>1.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>3.5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7">
+        <v>1.43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="M3" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2" location="event/1023224945"/>
+    <hyperlink ref="N3" r:id="rId2"/>
     <hyperlink ref="M4" r:id="rId3"/>
     <hyperlink ref="N4" r:id="rId4" location="event/1023224945"/>
     <hyperlink ref="M5" r:id="rId5"/>
     <hyperlink ref="N5" r:id="rId6" location="event/1023224945"/>
     <hyperlink ref="M6" r:id="rId7"/>
     <hyperlink ref="N6" r:id="rId8" location="event/1023224945"/>
+    <hyperlink ref="M7" r:id="rId9"/>
+    <hyperlink ref="N7" r:id="rId10" location="event/1023224945"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Advies.xlsx
+++ b/data/Advies.xlsx
@@ -58,7 +58,7 @@
     <t>Link 2</t>
   </si>
   <si>
-    <t>Laatst bijgewerkt: 2025-09-06 19:17:39</t>
+    <t>Laatst bijgewerkt: 2025-09-06 19:19:41</t>
   </si>
   <si>
     <t>Duitsland vs Noord-Ierland</t>
